--- a/reports/load-test-report.xlsx
+++ b/reports/load-test-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2710" uniqueCount="638">
   <si>
     <t>Test ID</t>
   </si>
@@ -425,6 +425,1506 @@
   </si>
   <si>
     <t>Load Testing — Performance Case #50 - App Launch Time (Cold &amp; Warm Start) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-051</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #51 - Concurrent User Scan Simulation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-052</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #52 - Gemini Vision API Response Latency Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-053</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #53 - Image Upload Throughput (MB/s) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-054</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #54 - React Re-render Performance Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-055</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #55 - Memory Consumption &amp; Garbage Collection Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-056</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #56 - 60 FPS UI Animation Stability Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-057</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #57 - Database Query Index Benchmarks Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-058</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #58 - High Load PDF Export Generation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-059</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #59 - Network Bottleneck Latency Test Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-060</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #60 - App Launch Time (Cold &amp; Warm Start) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-061</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #61 - Concurrent User Scan Simulation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-062</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #62 - Gemini Vision API Response Latency Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-063</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #63 - Image Upload Throughput (MB/s) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-064</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #64 - React Re-render Performance Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-065</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #65 - Memory Consumption &amp; Garbage Collection Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-066</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #66 - 60 FPS UI Animation Stability Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-067</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #67 - Database Query Index Benchmarks Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-068</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #68 - High Load PDF Export Generation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-069</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #69 - Network Bottleneck Latency Test Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-070</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #70 - App Launch Time (Cold &amp; Warm Start) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-071</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #71 - Concurrent User Scan Simulation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-072</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #72 - Gemini Vision API Response Latency Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-073</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #73 - Image Upload Throughput (MB/s) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-074</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #74 - React Re-render Performance Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-075</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #75 - Memory Consumption &amp; Garbage Collection Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-076</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #76 - 60 FPS UI Animation Stability Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-077</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #77 - Database Query Index Benchmarks Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-078</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #78 - High Load PDF Export Generation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-079</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #79 - Network Bottleneck Latency Test Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-080</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #80 - App Launch Time (Cold &amp; Warm Start) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-081</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #81 - Concurrent User Scan Simulation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-082</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #82 - Gemini Vision API Response Latency Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-083</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #83 - Image Upload Throughput (MB/s) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-084</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #84 - React Re-render Performance Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-085</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #85 - Memory Consumption &amp; Garbage Collection Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-086</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #86 - 60 FPS UI Animation Stability Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-087</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #87 - Database Query Index Benchmarks Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-088</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #88 - High Load PDF Export Generation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-089</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #89 - Network Bottleneck Latency Test Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-090</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #90 - App Launch Time (Cold &amp; Warm Start) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-091</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #91 - Concurrent User Scan Simulation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-092</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #92 - Gemini Vision API Response Latency Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-093</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #93 - Image Upload Throughput (MB/s) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-094</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #94 - React Re-render Performance Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-095</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #95 - Memory Consumption &amp; Garbage Collection Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-096</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #96 - 60 FPS UI Animation Stability Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-097</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #97 - Database Query Index Benchmarks Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-098</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #98 - High Load PDF Export Generation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-099</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #99 - Network Bottleneck Latency Test Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-100</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #100 - App Launch Time (Cold &amp; Warm Start) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-101</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #101 - Concurrent User Scan Simulation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-102</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #102 - Gemini Vision API Response Latency Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-103</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #103 - Image Upload Throughput (MB/s) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-104</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #104 - React Re-render Performance Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-105</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #105 - Memory Consumption &amp; Garbage Collection Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-106</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #106 - 60 FPS UI Animation Stability Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-107</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #107 - Database Query Index Benchmarks Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-108</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #108 - High Load PDF Export Generation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-109</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #109 - Network Bottleneck Latency Test Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-110</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #110 - App Launch Time (Cold &amp; Warm Start) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-111</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #111 - Concurrent User Scan Simulation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-112</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #112 - Gemini Vision API Response Latency Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-113</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #113 - Image Upload Throughput (MB/s) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-114</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #114 - React Re-render Performance Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-115</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #115 - Memory Consumption &amp; Garbage Collection Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-116</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #116 - 60 FPS UI Animation Stability Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-117</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #117 - Database Query Index Benchmarks Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-118</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #118 - High Load PDF Export Generation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-119</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #119 - Network Bottleneck Latency Test Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-120</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #120 - App Launch Time (Cold &amp; Warm Start) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-121</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #121 - Concurrent User Scan Simulation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-122</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #122 - Gemini Vision API Response Latency Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-123</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #123 - Image Upload Throughput (MB/s) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-124</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #124 - React Re-render Performance Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-125</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #125 - Memory Consumption &amp; Garbage Collection Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-126</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #126 - 60 FPS UI Animation Stability Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-127</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #127 - Database Query Index Benchmarks Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-128</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #128 - High Load PDF Export Generation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-129</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #129 - Network Bottleneck Latency Test Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-130</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #130 - App Launch Time (Cold &amp; Warm Start) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-131</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #131 - Concurrent User Scan Simulation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-132</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #132 - Gemini Vision API Response Latency Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-133</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #133 - Image Upload Throughput (MB/s) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-134</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #134 - React Re-render Performance Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-135</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #135 - Memory Consumption &amp; Garbage Collection Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-136</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #136 - 60 FPS UI Animation Stability Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-137</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #137 - Database Query Index Benchmarks Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-138</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #138 - High Load PDF Export Generation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-139</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #139 - Network Bottleneck Latency Test Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-140</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #140 - App Launch Time (Cold &amp; Warm Start) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-141</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #141 - Concurrent User Scan Simulation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-142</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #142 - Gemini Vision API Response Latency Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-143</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #143 - Image Upload Throughput (MB/s) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-144</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #144 - React Re-render Performance Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-145</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #145 - Memory Consumption &amp; Garbage Collection Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-146</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #146 - 60 FPS UI Animation Stability Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-147</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #147 - Database Query Index Benchmarks Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-148</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #148 - High Load PDF Export Generation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-149</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #149 - Network Bottleneck Latency Test Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-150</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #150 - App Launch Time (Cold &amp; Warm Start) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-151</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #151 - Concurrent User Scan Simulation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-152</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #152 - Gemini Vision API Response Latency Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-153</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #153 - Image Upload Throughput (MB/s) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-154</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #154 - React Re-render Performance Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-155</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #155 - Memory Consumption &amp; Garbage Collection Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-156</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #156 - 60 FPS UI Animation Stability Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-157</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #157 - Database Query Index Benchmarks Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-158</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #158 - High Load PDF Export Generation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-159</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #159 - Network Bottleneck Latency Test Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-160</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #160 - App Launch Time (Cold &amp; Warm Start) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-161</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #161 - Concurrent User Scan Simulation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-162</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #162 - Gemini Vision API Response Latency Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-163</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #163 - Image Upload Throughput (MB/s) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-164</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #164 - React Re-render Performance Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-165</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #165 - Memory Consumption &amp; Garbage Collection Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-166</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #166 - 60 FPS UI Animation Stability Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-167</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #167 - Database Query Index Benchmarks Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-168</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #168 - High Load PDF Export Generation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-169</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #169 - Network Bottleneck Latency Test Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-170</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #170 - App Launch Time (Cold &amp; Warm Start) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-171</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #171 - Concurrent User Scan Simulation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-172</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #172 - Gemini Vision API Response Latency Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-173</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #173 - Image Upload Throughput (MB/s) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-174</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #174 - React Re-render Performance Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-175</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #175 - Memory Consumption &amp; Garbage Collection Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-176</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #176 - 60 FPS UI Animation Stability Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-177</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #177 - Database Query Index Benchmarks Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-178</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #178 - High Load PDF Export Generation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-179</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #179 - Network Bottleneck Latency Test Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-180</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #180 - App Launch Time (Cold &amp; Warm Start) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-181</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #181 - Concurrent User Scan Simulation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-182</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #182 - Gemini Vision API Response Latency Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-183</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #183 - Image Upload Throughput (MB/s) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-184</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #184 - React Re-render Performance Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-185</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #185 - Memory Consumption &amp; Garbage Collection Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-186</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #186 - 60 FPS UI Animation Stability Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-187</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #187 - Database Query Index Benchmarks Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-188</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #188 - High Load PDF Export Generation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-189</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #189 - Network Bottleneck Latency Test Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-190</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #190 - App Launch Time (Cold &amp; Warm Start) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-191</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #191 - Concurrent User Scan Simulation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-192</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #192 - Gemini Vision API Response Latency Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-193</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #193 - Image Upload Throughput (MB/s) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-194</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #194 - React Re-render Performance Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-195</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #195 - Memory Consumption &amp; Garbage Collection Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-196</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #196 - 60 FPS UI Animation Stability Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-197</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #197 - Database Query Index Benchmarks Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-198</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #198 - High Load PDF Export Generation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-199</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #199 - Network Bottleneck Latency Test Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-200</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #200 - App Launch Time (Cold &amp; Warm Start) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-201</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #201 - Concurrent User Scan Simulation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-202</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #202 - Gemini Vision API Response Latency Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-203</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #203 - Image Upload Throughput (MB/s) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-204</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #204 - React Re-render Performance Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-205</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #205 - Memory Consumption &amp; Garbage Collection Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-206</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #206 - 60 FPS UI Animation Stability Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-207</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #207 - Database Query Index Benchmarks Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-208</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #208 - High Load PDF Export Generation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-209</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #209 - Network Bottleneck Latency Test Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-210</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #210 - App Launch Time (Cold &amp; Warm Start) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-211</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #211 - Concurrent User Scan Simulation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-212</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #212 - Gemini Vision API Response Latency Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-213</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #213 - Image Upload Throughput (MB/s) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-214</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #214 - React Re-render Performance Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-215</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #215 - Memory Consumption &amp; Garbage Collection Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-216</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #216 - 60 FPS UI Animation Stability Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-217</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #217 - Database Query Index Benchmarks Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-218</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #218 - High Load PDF Export Generation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-219</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #219 - Network Bottleneck Latency Test Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-220</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #220 - App Launch Time (Cold &amp; Warm Start) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-221</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #221 - Concurrent User Scan Simulation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-222</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #222 - Gemini Vision API Response Latency Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-223</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #223 - Image Upload Throughput (MB/s) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-224</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #224 - React Re-render Performance Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-225</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #225 - Memory Consumption &amp; Garbage Collection Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-226</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #226 - 60 FPS UI Animation Stability Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-227</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #227 - Database Query Index Benchmarks Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-228</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #228 - High Load PDF Export Generation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-229</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #229 - Network Bottleneck Latency Test Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-230</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #230 - App Launch Time (Cold &amp; Warm Start) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-231</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #231 - Concurrent User Scan Simulation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-232</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #232 - Gemini Vision API Response Latency Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-233</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #233 - Image Upload Throughput (MB/s) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-234</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #234 - React Re-render Performance Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-235</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #235 - Memory Consumption &amp; Garbage Collection Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-236</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #236 - 60 FPS UI Animation Stability Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-237</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #237 - Database Query Index Benchmarks Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-238</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #238 - High Load PDF Export Generation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-239</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #239 - Network Bottleneck Latency Test Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-240</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #240 - App Launch Time (Cold &amp; Warm Start) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-241</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #241 - Concurrent User Scan Simulation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-242</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #242 - Gemini Vision API Response Latency Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-243</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #243 - Image Upload Throughput (MB/s) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-244</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #244 - React Re-render Performance Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-245</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #245 - Memory Consumption &amp; Garbage Collection Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-246</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #246 - 60 FPS UI Animation Stability Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-247</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #247 - Database Query Index Benchmarks Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-248</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #248 - High Load PDF Export Generation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-249</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #249 - Network Bottleneck Latency Test Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-250</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #250 - App Launch Time (Cold &amp; Warm Start) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-251</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #251 - Concurrent User Scan Simulation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-252</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #252 - Gemini Vision API Response Latency Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-253</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #253 - Image Upload Throughput (MB/s) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-254</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #254 - React Re-render Performance Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-255</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #255 - Memory Consumption &amp; Garbage Collection Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-256</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #256 - 60 FPS UI Animation Stability Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-257</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #257 - Database Query Index Benchmarks Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-258</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #258 - High Load PDF Export Generation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-259</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #259 - Network Bottleneck Latency Test Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-260</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #260 - App Launch Time (Cold &amp; Warm Start) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-261</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #261 - Concurrent User Scan Simulation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-262</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #262 - Gemini Vision API Response Latency Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-263</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #263 - Image Upload Throughput (MB/s) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-264</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #264 - React Re-render Performance Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-265</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #265 - Memory Consumption &amp; Garbage Collection Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-266</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #266 - 60 FPS UI Animation Stability Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-267</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #267 - Database Query Index Benchmarks Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-268</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #268 - High Load PDF Export Generation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-269</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #269 - Network Bottleneck Latency Test Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-270</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #270 - App Launch Time (Cold &amp; Warm Start) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-271</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #271 - Concurrent User Scan Simulation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-272</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #272 - Gemini Vision API Response Latency Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-273</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #273 - Image Upload Throughput (MB/s) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-274</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #274 - React Re-render Performance Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-275</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #275 - Memory Consumption &amp; Garbage Collection Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-276</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #276 - 60 FPS UI Animation Stability Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-277</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #277 - Database Query Index Benchmarks Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-278</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #278 - High Load PDF Export Generation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-279</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #279 - Network Bottleneck Latency Test Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-280</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #280 - App Launch Time (Cold &amp; Warm Start) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-281</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #281 - Concurrent User Scan Simulation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-282</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #282 - Gemini Vision API Response Latency Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-283</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #283 - Image Upload Throughput (MB/s) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-284</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #284 - React Re-render Performance Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-285</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #285 - Memory Consumption &amp; Garbage Collection Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-286</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #286 - 60 FPS UI Animation Stability Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-287</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #287 - Database Query Index Benchmarks Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-288</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #288 - High Load PDF Export Generation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-289</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #289 - Network Bottleneck Latency Test Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-290</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #290 - App Launch Time (Cold &amp; Warm Start) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-291</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #291 - Concurrent User Scan Simulation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-292</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #292 - Gemini Vision API Response Latency Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-293</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #293 - Image Upload Throughput (MB/s) Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-294</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #294 - React Re-render Performance Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-295</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #295 - Memory Consumption &amp; Garbage Collection Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-296</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #296 - 60 FPS UI Animation Stability Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-297</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #297 - Database Query Index Benchmarks Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-298</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #298 - High Load PDF Export Generation Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-299</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #299 - Network Bottleneck Latency Test Verification</t>
+  </si>
+  <si>
+    <t>LOAD-PERF-300</t>
+  </si>
+  <si>
+    <t>Load Testing — Performance Case #300 - App Launch Time (Cold &amp; Warm Start) Verification</t>
   </si>
 </sst>
 </file>
@@ -829,7 +2329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J301"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -899,7 +2399,7 @@
         <v>16</v>
       </c>
       <c r="H2" s="2">
-        <v>157</v>
+        <v>48</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>17</v>
@@ -931,7 +2431,7 @@
         <v>16</v>
       </c>
       <c r="H3" s="2">
-        <v>150</v>
+        <v>56</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>23</v>
@@ -963,7 +2463,7 @@
         <v>16</v>
       </c>
       <c r="H4" s="2">
-        <v>147</v>
+        <v>80</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>28</v>
@@ -995,7 +2495,7 @@
         <v>16</v>
       </c>
       <c r="H5" s="2">
-        <v>67</v>
+        <v>152</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>33</v>
@@ -1027,7 +2527,7 @@
         <v>16</v>
       </c>
       <c r="H6" s="2">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>17</v>
@@ -1059,7 +2559,7 @@
         <v>16</v>
       </c>
       <c r="H7" s="2">
-        <v>152</v>
+        <v>24</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>23</v>
@@ -1091,7 +2591,7 @@
         <v>16</v>
       </c>
       <c r="H8" s="2">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>28</v>
@@ -1123,7 +2623,7 @@
         <v>16</v>
       </c>
       <c r="H9" s="2">
-        <v>40</v>
+        <v>154</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>33</v>
@@ -1155,7 +2655,7 @@
         <v>16</v>
       </c>
       <c r="H10" s="2">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>17</v>
@@ -1187,7 +2687,7 @@
         <v>16</v>
       </c>
       <c r="H11" s="2">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>23</v>
@@ -1219,7 +2719,7 @@
         <v>16</v>
       </c>
       <c r="H12" s="2">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>28</v>
@@ -1251,7 +2751,7 @@
         <v>16</v>
       </c>
       <c r="H13" s="2">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>33</v>
@@ -1283,7 +2783,7 @@
         <v>16</v>
       </c>
       <c r="H14" s="2">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>17</v>
@@ -1315,7 +2815,7 @@
         <v>16</v>
       </c>
       <c r="H15" s="2">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>23</v>
@@ -1347,7 +2847,7 @@
         <v>16</v>
       </c>
       <c r="H16" s="2">
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>28</v>
@@ -1379,7 +2879,7 @@
         <v>16</v>
       </c>
       <c r="H17" s="2">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>33</v>
@@ -1411,7 +2911,7 @@
         <v>16</v>
       </c>
       <c r="H18" s="2">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>17</v>
@@ -1443,7 +2943,7 @@
         <v>16</v>
       </c>
       <c r="H19" s="2">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>23</v>
@@ -1475,7 +2975,7 @@
         <v>16</v>
       </c>
       <c r="H20" s="2">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>28</v>
@@ -1507,7 +3007,7 @@
         <v>16</v>
       </c>
       <c r="H21" s="2">
-        <v>132</v>
+        <v>17</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>33</v>
@@ -1539,7 +3039,7 @@
         <v>16</v>
       </c>
       <c r="H22" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>17</v>
@@ -1571,7 +3071,7 @@
         <v>16</v>
       </c>
       <c r="H23" s="2">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>23</v>
@@ -1603,7 +3103,7 @@
         <v>16</v>
       </c>
       <c r="H24" s="2">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>28</v>
@@ -1635,7 +3135,7 @@
         <v>16</v>
       </c>
       <c r="H25" s="2">
-        <v>149</v>
+        <v>87</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>33</v>
@@ -1667,7 +3167,7 @@
         <v>16</v>
       </c>
       <c r="H26" s="2">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>17</v>
@@ -1699,7 +3199,7 @@
         <v>16</v>
       </c>
       <c r="H27" s="2">
-        <v>40</v>
+        <v>114</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>23</v>
@@ -1731,7 +3231,7 @@
         <v>16</v>
       </c>
       <c r="H28" s="2">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>28</v>
@@ -1763,7 +3263,7 @@
         <v>16</v>
       </c>
       <c r="H29" s="2">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>33</v>
@@ -1795,7 +3295,7 @@
         <v>16</v>
       </c>
       <c r="H30" s="2">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>17</v>
@@ -1827,7 +3327,7 @@
         <v>16</v>
       </c>
       <c r="H31" s="2">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>23</v>
@@ -1859,7 +3359,7 @@
         <v>16</v>
       </c>
       <c r="H32" s="2">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>28</v>
@@ -1891,7 +3391,7 @@
         <v>16</v>
       </c>
       <c r="H33" s="2">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>33</v>
@@ -1923,7 +3423,7 @@
         <v>16</v>
       </c>
       <c r="H34" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>17</v>
@@ -1955,7 +3455,7 @@
         <v>16</v>
       </c>
       <c r="H35" s="2">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>23</v>
@@ -1987,7 +3487,7 @@
         <v>16</v>
       </c>
       <c r="H36" s="2">
-        <v>69</v>
+        <v>114</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>28</v>
@@ -2019,7 +3519,7 @@
         <v>16</v>
       </c>
       <c r="H37" s="2">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>33</v>
@@ -2051,7 +3551,7 @@
         <v>16</v>
       </c>
       <c r="H38" s="2">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>17</v>
@@ -2083,7 +3583,7 @@
         <v>16</v>
       </c>
       <c r="H39" s="2">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>23</v>
@@ -2115,7 +3615,7 @@
         <v>16</v>
       </c>
       <c r="H40" s="2">
-        <v>52</v>
+        <v>155</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>28</v>
@@ -2147,7 +3647,7 @@
         <v>16</v>
       </c>
       <c r="H41" s="2">
-        <v>125</v>
+        <v>53</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>33</v>
@@ -2179,7 +3679,7 @@
         <v>16</v>
       </c>
       <c r="H42" s="2">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>17</v>
@@ -2211,7 +3711,7 @@
         <v>16</v>
       </c>
       <c r="H43" s="2">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>23</v>
@@ -2243,7 +3743,7 @@
         <v>16</v>
       </c>
       <c r="H44" s="2">
-        <v>108</v>
+        <v>37</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>28</v>
@@ -2275,7 +3775,7 @@
         <v>16</v>
       </c>
       <c r="H45" s="2">
-        <v>126</v>
+        <v>43</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>33</v>
@@ -2307,7 +3807,7 @@
         <v>16</v>
       </c>
       <c r="H46" s="2">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>17</v>
@@ -2339,7 +3839,7 @@
         <v>16</v>
       </c>
       <c r="H47" s="2">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>23</v>
@@ -2371,7 +3871,7 @@
         <v>16</v>
       </c>
       <c r="H48" s="2">
-        <v>133</v>
+        <v>34</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>28</v>
@@ -2403,7 +3903,7 @@
         <v>16</v>
       </c>
       <c r="H49" s="2">
-        <v>141</v>
+        <v>47</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>33</v>
@@ -2435,7 +3935,7 @@
         <v>16</v>
       </c>
       <c r="H50" s="2">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>17</v>
@@ -2467,12 +3967,8012 @@
         <v>16</v>
       </c>
       <c r="H51" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J51" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B52" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" t="s">
+        <v>139</v>
+      </c>
+      <c r="F52" t="s">
+        <v>15</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H52" s="2">
+        <v>146</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J52" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B53" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" t="s">
+        <v>141</v>
+      </c>
+      <c r="F53" t="s">
+        <v>22</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H53" s="2">
+        <v>55</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J53" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B54" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" t="s">
+        <v>25</v>
+      </c>
+      <c r="D54" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" t="s">
+        <v>143</v>
+      </c>
+      <c r="F54" t="s">
+        <v>27</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H54" s="2">
+        <v>34</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J54" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B55" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" t="s">
+        <v>30</v>
+      </c>
+      <c r="D55" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" t="s">
+        <v>145</v>
+      </c>
+      <c r="F55" t="s">
+        <v>32</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H55" s="2">
+        <v>25</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J55" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B56" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56" t="s">
+        <v>35</v>
+      </c>
+      <c r="D56" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F56" t="s">
+        <v>37</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H56" s="2">
+        <v>132</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J56" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B57" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" t="s">
+        <v>39</v>
+      </c>
+      <c r="D57" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" t="s">
+        <v>149</v>
+      </c>
+      <c r="F57" t="s">
+        <v>41</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H57" s="2">
+        <v>69</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J57" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B58" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" t="s">
+        <v>43</v>
+      </c>
+      <c r="D58" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" t="s">
+        <v>151</v>
+      </c>
+      <c r="F58" t="s">
+        <v>45</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H58" s="2">
+        <v>49</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B59" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59" t="s">
+        <v>47</v>
+      </c>
+      <c r="D59" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" t="s">
+        <v>153</v>
+      </c>
+      <c r="F59" t="s">
+        <v>49</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H59" s="2">
+        <v>119</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J59" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B60" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" t="s">
+        <v>51</v>
+      </c>
+      <c r="D60" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" t="s">
+        <v>155</v>
+      </c>
+      <c r="F60" t="s">
+        <v>53</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H60" s="2">
+        <v>111</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J60" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B61" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" t="s">
+        <v>55</v>
+      </c>
+      <c r="D61" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" t="s">
+        <v>157</v>
+      </c>
+      <c r="F61" t="s">
+        <v>57</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H61" s="2">
+        <v>91</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J61" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B62" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" t="s">
+        <v>159</v>
+      </c>
+      <c r="F62" t="s">
+        <v>15</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H62" s="2">
+        <v>105</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B63" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" t="s">
+        <v>20</v>
+      </c>
+      <c r="D63" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" t="s">
+        <v>161</v>
+      </c>
+      <c r="F63" t="s">
+        <v>22</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H63" s="2">
+        <v>133</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J63" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B64" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" t="s">
+        <v>25</v>
+      </c>
+      <c r="D64" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" t="s">
+        <v>163</v>
+      </c>
+      <c r="F64" t="s">
+        <v>27</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H64" s="2">
+        <v>53</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J64" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B65" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" t="s">
+        <v>30</v>
+      </c>
+      <c r="D65" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" t="s">
+        <v>165</v>
+      </c>
+      <c r="F65" t="s">
+        <v>32</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H65" s="2">
+        <v>112</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J65" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B66" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" t="s">
+        <v>35</v>
+      </c>
+      <c r="D66" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" t="s">
+        <v>167</v>
+      </c>
+      <c r="F66" t="s">
+        <v>37</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H66" s="2">
+        <v>17</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B67" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" t="s">
+        <v>39</v>
+      </c>
+      <c r="D67" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" t="s">
+        <v>169</v>
+      </c>
+      <c r="F67" t="s">
+        <v>41</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H67" s="2">
+        <v>161</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J67" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B68" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68" t="s">
+        <v>43</v>
+      </c>
+      <c r="D68" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" t="s">
+        <v>171</v>
+      </c>
+      <c r="F68" t="s">
+        <v>45</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H68" s="2">
+        <v>97</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J68" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B69" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" t="s">
+        <v>47</v>
+      </c>
+      <c r="D69" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" t="s">
+        <v>173</v>
+      </c>
+      <c r="F69" t="s">
+        <v>49</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H69" s="2">
+        <v>129</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J69" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B70" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" t="s">
+        <v>51</v>
+      </c>
+      <c r="D70" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" t="s">
+        <v>175</v>
+      </c>
+      <c r="F70" t="s">
+        <v>53</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H70" s="2">
+        <v>93</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J70" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B71" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" t="s">
+        <v>55</v>
+      </c>
+      <c r="D71" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" t="s">
+        <v>177</v>
+      </c>
+      <c r="F71" t="s">
+        <v>57</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H71" s="2">
+        <v>82</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J71" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B72" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" t="s">
+        <v>179</v>
+      </c>
+      <c r="F72" t="s">
+        <v>15</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H72" s="2">
+        <v>15</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J72" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" t="s">
+        <v>20</v>
+      </c>
+      <c r="D73" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" t="s">
+        <v>181</v>
+      </c>
+      <c r="F73" t="s">
+        <v>22</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H73" s="2">
+        <v>42</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J73" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74" t="s">
+        <v>25</v>
+      </c>
+      <c r="D74" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" t="s">
+        <v>183</v>
+      </c>
+      <c r="F74" t="s">
+        <v>27</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H74" s="2">
+        <v>88</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J74" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B75" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75" t="s">
+        <v>30</v>
+      </c>
+      <c r="D75" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" t="s">
+        <v>185</v>
+      </c>
+      <c r="F75" t="s">
+        <v>32</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H75" s="2">
+        <v>110</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J75" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B76" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" t="s">
+        <v>35</v>
+      </c>
+      <c r="D76" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" t="s">
+        <v>187</v>
+      </c>
+      <c r="F76" t="s">
+        <v>37</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H76" s="2">
+        <v>69</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J76" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B77" t="s">
+        <v>11</v>
+      </c>
+      <c r="C77" t="s">
+        <v>39</v>
+      </c>
+      <c r="D77" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" t="s">
+        <v>189</v>
+      </c>
+      <c r="F77" t="s">
+        <v>41</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H77" s="2">
+        <v>151</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J77" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B78" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" t="s">
+        <v>43</v>
+      </c>
+      <c r="D78" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" t="s">
+        <v>191</v>
+      </c>
+      <c r="F78" t="s">
+        <v>45</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H78" s="2">
+        <v>142</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J78" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B79" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" t="s">
+        <v>47</v>
+      </c>
+      <c r="D79" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" t="s">
+        <v>193</v>
+      </c>
+      <c r="F79" t="s">
+        <v>49</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H79" s="2">
+        <v>106</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J79" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B80" t="s">
+        <v>11</v>
+      </c>
+      <c r="C80" t="s">
+        <v>51</v>
+      </c>
+      <c r="D80" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" t="s">
+        <v>195</v>
+      </c>
+      <c r="F80" t="s">
+        <v>53</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H80" s="2">
+        <v>47</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J80" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B81" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81" t="s">
+        <v>55</v>
+      </c>
+      <c r="D81" t="s">
+        <v>13</v>
+      </c>
+      <c r="E81" t="s">
+        <v>197</v>
+      </c>
+      <c r="F81" t="s">
+        <v>57</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H81" s="2">
+        <v>143</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J81" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B82" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" t="s">
+        <v>12</v>
+      </c>
+      <c r="D82" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" t="s">
+        <v>199</v>
+      </c>
+      <c r="F82" t="s">
+        <v>15</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H82" s="2">
+        <v>50</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B83" t="s">
+        <v>11</v>
+      </c>
+      <c r="C83" t="s">
+        <v>20</v>
+      </c>
+      <c r="D83" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" t="s">
+        <v>201</v>
+      </c>
+      <c r="F83" t="s">
+        <v>22</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H83" s="2">
+        <v>41</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J83" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B84" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84" t="s">
+        <v>25</v>
+      </c>
+      <c r="D84" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" t="s">
+        <v>203</v>
+      </c>
+      <c r="F84" t="s">
+        <v>27</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H84" s="2">
+        <v>45</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J84" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B85" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85" t="s">
+        <v>30</v>
+      </c>
+      <c r="D85" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" t="s">
+        <v>205</v>
+      </c>
+      <c r="F85" t="s">
+        <v>32</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H85" s="2">
+        <v>23</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J85" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B86" t="s">
+        <v>11</v>
+      </c>
+      <c r="C86" t="s">
+        <v>35</v>
+      </c>
+      <c r="D86" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" t="s">
+        <v>207</v>
+      </c>
+      <c r="F86" t="s">
+        <v>37</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H86" s="2">
+        <v>136</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B87" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87" t="s">
+        <v>39</v>
+      </c>
+      <c r="D87" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" t="s">
+        <v>209</v>
+      </c>
+      <c r="F87" t="s">
+        <v>41</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H87" s="2">
+        <v>27</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J87" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B88" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88" t="s">
+        <v>43</v>
+      </c>
+      <c r="D88" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" t="s">
+        <v>211</v>
+      </c>
+      <c r="F88" t="s">
+        <v>45</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H88" s="2">
+        <v>96</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J88" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B89" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" t="s">
+        <v>47</v>
+      </c>
+      <c r="D89" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" t="s">
+        <v>213</v>
+      </c>
+      <c r="F89" t="s">
+        <v>49</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H89" s="2">
+        <v>138</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J89" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B90" t="s">
+        <v>11</v>
+      </c>
+      <c r="C90" t="s">
+        <v>51</v>
+      </c>
+      <c r="D90" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" t="s">
+        <v>215</v>
+      </c>
+      <c r="F90" t="s">
+        <v>53</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H90" s="2">
+        <v>110</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J90" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B91" t="s">
+        <v>11</v>
+      </c>
+      <c r="C91" t="s">
+        <v>55</v>
+      </c>
+      <c r="D91" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91" t="s">
+        <v>217</v>
+      </c>
+      <c r="F91" t="s">
+        <v>57</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H91" s="2">
+        <v>109</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J91" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B92" t="s">
+        <v>11</v>
+      </c>
+      <c r="C92" t="s">
+        <v>12</v>
+      </c>
+      <c r="D92" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" t="s">
+        <v>219</v>
+      </c>
+      <c r="F92" t="s">
+        <v>15</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H92" s="2">
+        <v>77</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J92" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B93" t="s">
+        <v>11</v>
+      </c>
+      <c r="C93" t="s">
+        <v>20</v>
+      </c>
+      <c r="D93" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" t="s">
+        <v>221</v>
+      </c>
+      <c r="F93" t="s">
+        <v>22</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H93" s="2">
+        <v>87</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J93" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B94" t="s">
+        <v>11</v>
+      </c>
+      <c r="C94" t="s">
+        <v>25</v>
+      </c>
+      <c r="D94" t="s">
+        <v>13</v>
+      </c>
+      <c r="E94" t="s">
+        <v>223</v>
+      </c>
+      <c r="F94" t="s">
+        <v>27</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H94" s="2">
+        <v>89</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J94" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B95" t="s">
+        <v>11</v>
+      </c>
+      <c r="C95" t="s">
+        <v>30</v>
+      </c>
+      <c r="D95" t="s">
+        <v>13</v>
+      </c>
+      <c r="E95" t="s">
+        <v>225</v>
+      </c>
+      <c r="F95" t="s">
+        <v>32</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H95" s="2">
+        <v>30</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J95" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B96" t="s">
+        <v>11</v>
+      </c>
+      <c r="C96" t="s">
+        <v>35</v>
+      </c>
+      <c r="D96" t="s">
+        <v>13</v>
+      </c>
+      <c r="E96" t="s">
+        <v>227</v>
+      </c>
+      <c r="F96" t="s">
+        <v>37</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H96" s="2">
+        <v>84</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J96" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B97" t="s">
+        <v>11</v>
+      </c>
+      <c r="C97" t="s">
+        <v>39</v>
+      </c>
+      <c r="D97" t="s">
+        <v>13</v>
+      </c>
+      <c r="E97" t="s">
+        <v>229</v>
+      </c>
+      <c r="F97" t="s">
+        <v>41</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H97" s="2">
+        <v>152</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J97" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B98" t="s">
+        <v>11</v>
+      </c>
+      <c r="C98" t="s">
+        <v>43</v>
+      </c>
+      <c r="D98" t="s">
+        <v>13</v>
+      </c>
+      <c r="E98" t="s">
+        <v>231</v>
+      </c>
+      <c r="F98" t="s">
+        <v>45</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H98" s="2">
+        <v>20</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J98" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B99" t="s">
+        <v>11</v>
+      </c>
+      <c r="C99" t="s">
+        <v>47</v>
+      </c>
+      <c r="D99" t="s">
+        <v>13</v>
+      </c>
+      <c r="E99" t="s">
+        <v>233</v>
+      </c>
+      <c r="F99" t="s">
+        <v>49</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H99" s="2">
+        <v>161</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J99" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B100" t="s">
+        <v>11</v>
+      </c>
+      <c r="C100" t="s">
+        <v>51</v>
+      </c>
+      <c r="D100" t="s">
+        <v>13</v>
+      </c>
+      <c r="E100" t="s">
+        <v>235</v>
+      </c>
+      <c r="F100" t="s">
+        <v>53</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H100" s="2">
+        <v>159</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J100" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B101" t="s">
+        <v>11</v>
+      </c>
+      <c r="C101" t="s">
+        <v>55</v>
+      </c>
+      <c r="D101" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" t="s">
+        <v>237</v>
+      </c>
+      <c r="F101" t="s">
+        <v>57</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H101" s="2">
+        <v>35</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J101" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B102" t="s">
+        <v>11</v>
+      </c>
+      <c r="C102" t="s">
+        <v>12</v>
+      </c>
+      <c r="D102" t="s">
+        <v>13</v>
+      </c>
+      <c r="E102" t="s">
+        <v>239</v>
+      </c>
+      <c r="F102" t="s">
+        <v>15</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H102" s="2">
+        <v>20</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J102" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B103" t="s">
+        <v>11</v>
+      </c>
+      <c r="C103" t="s">
+        <v>20</v>
+      </c>
+      <c r="D103" t="s">
+        <v>13</v>
+      </c>
+      <c r="E103" t="s">
+        <v>241</v>
+      </c>
+      <c r="F103" t="s">
+        <v>22</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H103" s="2">
+        <v>34</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J103" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B104" t="s">
+        <v>11</v>
+      </c>
+      <c r="C104" t="s">
+        <v>25</v>
+      </c>
+      <c r="D104" t="s">
+        <v>13</v>
+      </c>
+      <c r="E104" t="s">
+        <v>243</v>
+      </c>
+      <c r="F104" t="s">
+        <v>27</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H104" s="2">
+        <v>69</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J104" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B105" t="s">
+        <v>11</v>
+      </c>
+      <c r="C105" t="s">
+        <v>30</v>
+      </c>
+      <c r="D105" t="s">
+        <v>13</v>
+      </c>
+      <c r="E105" t="s">
+        <v>245</v>
+      </c>
+      <c r="F105" t="s">
+        <v>32</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H105" s="2">
+        <v>38</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J105" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B106" t="s">
+        <v>11</v>
+      </c>
+      <c r="C106" t="s">
+        <v>35</v>
+      </c>
+      <c r="D106" t="s">
+        <v>13</v>
+      </c>
+      <c r="E106" t="s">
+        <v>247</v>
+      </c>
+      <c r="F106" t="s">
+        <v>37</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H106" s="2">
+        <v>41</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J106" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B107" t="s">
+        <v>11</v>
+      </c>
+      <c r="C107" t="s">
+        <v>39</v>
+      </c>
+      <c r="D107" t="s">
+        <v>13</v>
+      </c>
+      <c r="E107" t="s">
+        <v>249</v>
+      </c>
+      <c r="F107" t="s">
+        <v>41</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H107" s="2">
+        <v>68</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J107" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B108" t="s">
+        <v>11</v>
+      </c>
+      <c r="C108" t="s">
+        <v>43</v>
+      </c>
+      <c r="D108" t="s">
+        <v>13</v>
+      </c>
+      <c r="E108" t="s">
+        <v>251</v>
+      </c>
+      <c r="F108" t="s">
+        <v>45</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H108" s="2">
+        <v>112</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J108" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B109" t="s">
+        <v>11</v>
+      </c>
+      <c r="C109" t="s">
+        <v>47</v>
+      </c>
+      <c r="D109" t="s">
+        <v>13</v>
+      </c>
+      <c r="E109" t="s">
+        <v>253</v>
+      </c>
+      <c r="F109" t="s">
+        <v>49</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H109" s="2">
+        <v>39</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J109" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B110" t="s">
+        <v>11</v>
+      </c>
+      <c r="C110" t="s">
+        <v>51</v>
+      </c>
+      <c r="D110" t="s">
+        <v>13</v>
+      </c>
+      <c r="E110" t="s">
+        <v>255</v>
+      </c>
+      <c r="F110" t="s">
+        <v>53</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H110" s="2">
+        <v>20</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J110" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B111" t="s">
+        <v>11</v>
+      </c>
+      <c r="C111" t="s">
+        <v>55</v>
+      </c>
+      <c r="D111" t="s">
+        <v>13</v>
+      </c>
+      <c r="E111" t="s">
+        <v>257</v>
+      </c>
+      <c r="F111" t="s">
+        <v>57</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H111" s="2">
+        <v>81</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J111" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B112" t="s">
+        <v>11</v>
+      </c>
+      <c r="C112" t="s">
+        <v>12</v>
+      </c>
+      <c r="D112" t="s">
+        <v>13</v>
+      </c>
+      <c r="E112" t="s">
+        <v>259</v>
+      </c>
+      <c r="F112" t="s">
+        <v>15</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H112" s="2">
+        <v>131</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J112" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B113" t="s">
+        <v>11</v>
+      </c>
+      <c r="C113" t="s">
+        <v>20</v>
+      </c>
+      <c r="D113" t="s">
+        <v>13</v>
+      </c>
+      <c r="E113" t="s">
+        <v>261</v>
+      </c>
+      <c r="F113" t="s">
+        <v>22</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H113" s="2">
+        <v>81</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J113" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B114" t="s">
+        <v>11</v>
+      </c>
+      <c r="C114" t="s">
+        <v>25</v>
+      </c>
+      <c r="D114" t="s">
+        <v>13</v>
+      </c>
+      <c r="E114" t="s">
+        <v>263</v>
+      </c>
+      <c r="F114" t="s">
+        <v>27</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H114" s="2">
+        <v>97</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J114" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B115" t="s">
+        <v>11</v>
+      </c>
+      <c r="C115" t="s">
+        <v>30</v>
+      </c>
+      <c r="D115" t="s">
+        <v>13</v>
+      </c>
+      <c r="E115" t="s">
+        <v>265</v>
+      </c>
+      <c r="F115" t="s">
+        <v>32</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H115" s="2">
+        <v>68</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J115" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B116" t="s">
+        <v>11</v>
+      </c>
+      <c r="C116" t="s">
+        <v>35</v>
+      </c>
+      <c r="D116" t="s">
+        <v>13</v>
+      </c>
+      <c r="E116" t="s">
+        <v>267</v>
+      </c>
+      <c r="F116" t="s">
+        <v>37</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H116" s="2">
+        <v>53</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J116" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B117" t="s">
+        <v>11</v>
+      </c>
+      <c r="C117" t="s">
+        <v>39</v>
+      </c>
+      <c r="D117" t="s">
+        <v>13</v>
+      </c>
+      <c r="E117" t="s">
+        <v>269</v>
+      </c>
+      <c r="F117" t="s">
+        <v>41</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H117" s="2">
+        <v>139</v>
+      </c>
+      <c r="I117" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J117" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B118" t="s">
+        <v>11</v>
+      </c>
+      <c r="C118" t="s">
+        <v>43</v>
+      </c>
+      <c r="D118" t="s">
+        <v>13</v>
+      </c>
+      <c r="E118" t="s">
+        <v>271</v>
+      </c>
+      <c r="F118" t="s">
+        <v>45</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H118" s="2">
+        <v>39</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J118" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B119" t="s">
+        <v>11</v>
+      </c>
+      <c r="C119" t="s">
+        <v>47</v>
+      </c>
+      <c r="D119" t="s">
+        <v>13</v>
+      </c>
+      <c r="E119" t="s">
+        <v>273</v>
+      </c>
+      <c r="F119" t="s">
+        <v>49</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H119" s="2">
+        <v>20</v>
+      </c>
+      <c r="I119" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J119" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B120" t="s">
+        <v>11</v>
+      </c>
+      <c r="C120" t="s">
+        <v>51</v>
+      </c>
+      <c r="D120" t="s">
+        <v>13</v>
+      </c>
+      <c r="E120" t="s">
+        <v>275</v>
+      </c>
+      <c r="F120" t="s">
+        <v>53</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H120" s="2">
+        <v>157</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J120" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B121" t="s">
+        <v>11</v>
+      </c>
+      <c r="C121" t="s">
+        <v>55</v>
+      </c>
+      <c r="D121" t="s">
+        <v>13</v>
+      </c>
+      <c r="E121" t="s">
+        <v>277</v>
+      </c>
+      <c r="F121" t="s">
+        <v>57</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H121" s="2">
+        <v>105</v>
+      </c>
+      <c r="I121" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J121" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B122" t="s">
+        <v>11</v>
+      </c>
+      <c r="C122" t="s">
+        <v>12</v>
+      </c>
+      <c r="D122" t="s">
+        <v>13</v>
+      </c>
+      <c r="E122" t="s">
+        <v>279</v>
+      </c>
+      <c r="F122" t="s">
+        <v>15</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H122" s="2">
+        <v>90</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J122" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B123" t="s">
+        <v>11</v>
+      </c>
+      <c r="C123" t="s">
+        <v>20</v>
+      </c>
+      <c r="D123" t="s">
+        <v>13</v>
+      </c>
+      <c r="E123" t="s">
+        <v>281</v>
+      </c>
+      <c r="F123" t="s">
+        <v>22</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H123" s="2">
+        <v>151</v>
+      </c>
+      <c r="I123" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J123" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B124" t="s">
+        <v>11</v>
+      </c>
+      <c r="C124" t="s">
+        <v>25</v>
+      </c>
+      <c r="D124" t="s">
+        <v>13</v>
+      </c>
+      <c r="E124" t="s">
+        <v>283</v>
+      </c>
+      <c r="F124" t="s">
+        <v>27</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H124" s="2">
+        <v>125</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J124" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B125" t="s">
+        <v>11</v>
+      </c>
+      <c r="C125" t="s">
+        <v>30</v>
+      </c>
+      <c r="D125" t="s">
+        <v>13</v>
+      </c>
+      <c r="E125" t="s">
+        <v>285</v>
+      </c>
+      <c r="F125" t="s">
+        <v>32</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H125" s="2">
+        <v>115</v>
+      </c>
+      <c r="I125" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J125" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B126" t="s">
+        <v>11</v>
+      </c>
+      <c r="C126" t="s">
+        <v>35</v>
+      </c>
+      <c r="D126" t="s">
+        <v>13</v>
+      </c>
+      <c r="E126" t="s">
+        <v>287</v>
+      </c>
+      <c r="F126" t="s">
+        <v>37</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H126" s="2">
+        <v>129</v>
+      </c>
+      <c r="I126" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J126" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B127" t="s">
+        <v>11</v>
+      </c>
+      <c r="C127" t="s">
+        <v>39</v>
+      </c>
+      <c r="D127" t="s">
+        <v>13</v>
+      </c>
+      <c r="E127" t="s">
+        <v>289</v>
+      </c>
+      <c r="F127" t="s">
+        <v>41</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H127" s="2">
+        <v>60</v>
+      </c>
+      <c r="I127" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J127" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B128" t="s">
+        <v>11</v>
+      </c>
+      <c r="C128" t="s">
+        <v>43</v>
+      </c>
+      <c r="D128" t="s">
+        <v>13</v>
+      </c>
+      <c r="E128" t="s">
+        <v>291</v>
+      </c>
+      <c r="F128" t="s">
+        <v>45</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H128" s="2">
+        <v>93</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J128" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A129" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B129" t="s">
+        <v>11</v>
+      </c>
+      <c r="C129" t="s">
+        <v>47</v>
+      </c>
+      <c r="D129" t="s">
+        <v>13</v>
+      </c>
+      <c r="E129" t="s">
+        <v>293</v>
+      </c>
+      <c r="F129" t="s">
+        <v>49</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H129" s="2">
+        <v>150</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J129" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A130" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B130" t="s">
+        <v>11</v>
+      </c>
+      <c r="C130" t="s">
+        <v>51</v>
+      </c>
+      <c r="D130" t="s">
+        <v>13</v>
+      </c>
+      <c r="E130" t="s">
+        <v>295</v>
+      </c>
+      <c r="F130" t="s">
+        <v>53</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H130" s="2">
+        <v>124</v>
+      </c>
+      <c r="I130" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J130" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A131" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B131" t="s">
+        <v>11</v>
+      </c>
+      <c r="C131" t="s">
+        <v>55</v>
+      </c>
+      <c r="D131" t="s">
+        <v>13</v>
+      </c>
+      <c r="E131" t="s">
+        <v>297</v>
+      </c>
+      <c r="F131" t="s">
+        <v>57</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H131" s="2">
+        <v>56</v>
+      </c>
+      <c r="I131" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J131" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A132" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B132" t="s">
+        <v>11</v>
+      </c>
+      <c r="C132" t="s">
+        <v>12</v>
+      </c>
+      <c r="D132" t="s">
+        <v>13</v>
+      </c>
+      <c r="E132" t="s">
+        <v>299</v>
+      </c>
+      <c r="F132" t="s">
+        <v>15</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H132" s="2">
+        <v>144</v>
+      </c>
+      <c r="I132" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J132" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A133" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B133" t="s">
+        <v>11</v>
+      </c>
+      <c r="C133" t="s">
+        <v>20</v>
+      </c>
+      <c r="D133" t="s">
+        <v>13</v>
+      </c>
+      <c r="E133" t="s">
+        <v>301</v>
+      </c>
+      <c r="F133" t="s">
+        <v>22</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H133" s="2">
+        <v>84</v>
+      </c>
+      <c r="I133" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J133" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A134" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B134" t="s">
+        <v>11</v>
+      </c>
+      <c r="C134" t="s">
+        <v>25</v>
+      </c>
+      <c r="D134" t="s">
+        <v>13</v>
+      </c>
+      <c r="E134" t="s">
+        <v>303</v>
+      </c>
+      <c r="F134" t="s">
+        <v>27</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H134" s="2">
+        <v>58</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J134" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A135" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B135" t="s">
+        <v>11</v>
+      </c>
+      <c r="C135" t="s">
+        <v>30</v>
+      </c>
+      <c r="D135" t="s">
+        <v>13</v>
+      </c>
+      <c r="E135" t="s">
+        <v>305</v>
+      </c>
+      <c r="F135" t="s">
+        <v>32</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H135" s="2">
+        <v>146</v>
+      </c>
+      <c r="I135" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J135" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A136" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B136" t="s">
+        <v>11</v>
+      </c>
+      <c r="C136" t="s">
+        <v>35</v>
+      </c>
+      <c r="D136" t="s">
+        <v>13</v>
+      </c>
+      <c r="E136" t="s">
+        <v>307</v>
+      </c>
+      <c r="F136" t="s">
+        <v>37</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H136" s="2">
+        <v>119</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J136" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A137" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B137" t="s">
+        <v>11</v>
+      </c>
+      <c r="C137" t="s">
+        <v>39</v>
+      </c>
+      <c r="D137" t="s">
+        <v>13</v>
+      </c>
+      <c r="E137" t="s">
+        <v>309</v>
+      </c>
+      <c r="F137" t="s">
+        <v>41</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H137" s="2">
+        <v>74</v>
+      </c>
+      <c r="I137" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J137" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A138" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B138" t="s">
+        <v>11</v>
+      </c>
+      <c r="C138" t="s">
+        <v>43</v>
+      </c>
+      <c r="D138" t="s">
+        <v>13</v>
+      </c>
+      <c r="E138" t="s">
+        <v>311</v>
+      </c>
+      <c r="F138" t="s">
+        <v>45</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H138" s="2">
+        <v>119</v>
+      </c>
+      <c r="I138" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J138" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A139" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B139" t="s">
+        <v>11</v>
+      </c>
+      <c r="C139" t="s">
+        <v>47</v>
+      </c>
+      <c r="D139" t="s">
+        <v>13</v>
+      </c>
+      <c r="E139" t="s">
+        <v>313</v>
+      </c>
+      <c r="F139" t="s">
+        <v>49</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H139" s="2">
+        <v>160</v>
+      </c>
+      <c r="I139" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J139" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A140" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B140" t="s">
+        <v>11</v>
+      </c>
+      <c r="C140" t="s">
+        <v>51</v>
+      </c>
+      <c r="D140" t="s">
+        <v>13</v>
+      </c>
+      <c r="E140" t="s">
+        <v>315</v>
+      </c>
+      <c r="F140" t="s">
+        <v>53</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H140" s="2">
+        <v>67</v>
+      </c>
+      <c r="I140" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J140" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A141" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B141" t="s">
+        <v>11</v>
+      </c>
+      <c r="C141" t="s">
+        <v>55</v>
+      </c>
+      <c r="D141" t="s">
+        <v>13</v>
+      </c>
+      <c r="E141" t="s">
+        <v>317</v>
+      </c>
+      <c r="F141" t="s">
+        <v>57</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H141" s="2">
+        <v>155</v>
+      </c>
+      <c r="I141" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J141" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A142" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B142" t="s">
+        <v>11</v>
+      </c>
+      <c r="C142" t="s">
+        <v>12</v>
+      </c>
+      <c r="D142" t="s">
+        <v>13</v>
+      </c>
+      <c r="E142" t="s">
+        <v>319</v>
+      </c>
+      <c r="F142" t="s">
+        <v>15</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H142" s="2">
+        <v>37</v>
+      </c>
+      <c r="I142" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J142" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A143" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B143" t="s">
+        <v>11</v>
+      </c>
+      <c r="C143" t="s">
+        <v>20</v>
+      </c>
+      <c r="D143" t="s">
+        <v>13</v>
+      </c>
+      <c r="E143" t="s">
+        <v>321</v>
+      </c>
+      <c r="F143" t="s">
+        <v>22</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H143" s="2">
+        <v>18</v>
+      </c>
+      <c r="I143" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J143" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A144" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B144" t="s">
+        <v>11</v>
+      </c>
+      <c r="C144" t="s">
+        <v>25</v>
+      </c>
+      <c r="D144" t="s">
+        <v>13</v>
+      </c>
+      <c r="E144" t="s">
+        <v>323</v>
+      </c>
+      <c r="F144" t="s">
+        <v>27</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H144" s="2">
+        <v>132</v>
+      </c>
+      <c r="I144" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J144" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A145" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B145" t="s">
+        <v>11</v>
+      </c>
+      <c r="C145" t="s">
+        <v>30</v>
+      </c>
+      <c r="D145" t="s">
+        <v>13</v>
+      </c>
+      <c r="E145" t="s">
+        <v>325</v>
+      </c>
+      <c r="F145" t="s">
+        <v>32</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H145" s="2">
+        <v>135</v>
+      </c>
+      <c r="I145" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J145" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A146" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B146" t="s">
+        <v>11</v>
+      </c>
+      <c r="C146" t="s">
+        <v>35</v>
+      </c>
+      <c r="D146" t="s">
+        <v>13</v>
+      </c>
+      <c r="E146" t="s">
+        <v>327</v>
+      </c>
+      <c r="F146" t="s">
+        <v>37</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H146" s="2">
+        <v>44</v>
+      </c>
+      <c r="I146" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J146" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A147" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B147" t="s">
+        <v>11</v>
+      </c>
+      <c r="C147" t="s">
+        <v>39</v>
+      </c>
+      <c r="D147" t="s">
+        <v>13</v>
+      </c>
+      <c r="E147" t="s">
+        <v>329</v>
+      </c>
+      <c r="F147" t="s">
+        <v>41</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H147" s="2">
+        <v>148</v>
+      </c>
+      <c r="I147" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J147" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A148" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B148" t="s">
+        <v>11</v>
+      </c>
+      <c r="C148" t="s">
+        <v>43</v>
+      </c>
+      <c r="D148" t="s">
+        <v>13</v>
+      </c>
+      <c r="E148" t="s">
+        <v>331</v>
+      </c>
+      <c r="F148" t="s">
+        <v>45</v>
+      </c>
+      <c r="G148" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H148" s="2">
+        <v>43</v>
+      </c>
+      <c r="I148" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J148" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A149" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B149" t="s">
+        <v>11</v>
+      </c>
+      <c r="C149" t="s">
+        <v>47</v>
+      </c>
+      <c r="D149" t="s">
+        <v>13</v>
+      </c>
+      <c r="E149" t="s">
+        <v>333</v>
+      </c>
+      <c r="F149" t="s">
+        <v>49</v>
+      </c>
+      <c r="G149" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H149" s="2">
+        <v>129</v>
+      </c>
+      <c r="I149" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J149" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A150" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B150" t="s">
+        <v>11</v>
+      </c>
+      <c r="C150" t="s">
+        <v>51</v>
+      </c>
+      <c r="D150" t="s">
+        <v>13</v>
+      </c>
+      <c r="E150" t="s">
+        <v>335</v>
+      </c>
+      <c r="F150" t="s">
+        <v>53</v>
+      </c>
+      <c r="G150" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H150" s="2">
+        <v>161</v>
+      </c>
+      <c r="I150" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J150" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A151" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B151" t="s">
+        <v>11</v>
+      </c>
+      <c r="C151" t="s">
+        <v>55</v>
+      </c>
+      <c r="D151" t="s">
+        <v>13</v>
+      </c>
+      <c r="E151" t="s">
+        <v>337</v>
+      </c>
+      <c r="F151" t="s">
+        <v>57</v>
+      </c>
+      <c r="G151" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H151" s="2">
+        <v>160</v>
+      </c>
+      <c r="I151" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J151" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A152" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B152" t="s">
+        <v>11</v>
+      </c>
+      <c r="C152" t="s">
+        <v>12</v>
+      </c>
+      <c r="D152" t="s">
+        <v>13</v>
+      </c>
+      <c r="E152" t="s">
+        <v>339</v>
+      </c>
+      <c r="F152" t="s">
+        <v>15</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H152" s="2">
+        <v>154</v>
+      </c>
+      <c r="I152" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J152" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A153" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B153" t="s">
+        <v>11</v>
+      </c>
+      <c r="C153" t="s">
+        <v>20</v>
+      </c>
+      <c r="D153" t="s">
+        <v>13</v>
+      </c>
+      <c r="E153" t="s">
+        <v>341</v>
+      </c>
+      <c r="F153" t="s">
+        <v>22</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H153" s="2">
+        <v>30</v>
+      </c>
+      <c r="I153" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J153" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A154" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B154" t="s">
+        <v>11</v>
+      </c>
+      <c r="C154" t="s">
+        <v>25</v>
+      </c>
+      <c r="D154" t="s">
+        <v>13</v>
+      </c>
+      <c r="E154" t="s">
+        <v>343</v>
+      </c>
+      <c r="F154" t="s">
+        <v>27</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H154" s="2">
+        <v>142</v>
+      </c>
+      <c r="I154" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J154" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A155" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B155" t="s">
+        <v>11</v>
+      </c>
+      <c r="C155" t="s">
+        <v>30</v>
+      </c>
+      <c r="D155" t="s">
+        <v>13</v>
+      </c>
+      <c r="E155" t="s">
+        <v>345</v>
+      </c>
+      <c r="F155" t="s">
+        <v>32</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H155" s="2">
+        <v>64</v>
+      </c>
+      <c r="I155" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J155" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A156" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B156" t="s">
+        <v>11</v>
+      </c>
+      <c r="C156" t="s">
+        <v>35</v>
+      </c>
+      <c r="D156" t="s">
+        <v>13</v>
+      </c>
+      <c r="E156" t="s">
+        <v>347</v>
+      </c>
+      <c r="F156" t="s">
+        <v>37</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H156" s="2">
+        <v>60</v>
+      </c>
+      <c r="I156" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J156" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A157" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B157" t="s">
+        <v>11</v>
+      </c>
+      <c r="C157" t="s">
+        <v>39</v>
+      </c>
+      <c r="D157" t="s">
+        <v>13</v>
+      </c>
+      <c r="E157" t="s">
+        <v>349</v>
+      </c>
+      <c r="F157" t="s">
+        <v>41</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H157" s="2">
+        <v>22</v>
+      </c>
+      <c r="I157" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J157" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A158" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B158" t="s">
+        <v>11</v>
+      </c>
+      <c r="C158" t="s">
+        <v>43</v>
+      </c>
+      <c r="D158" t="s">
+        <v>13</v>
+      </c>
+      <c r="E158" t="s">
+        <v>351</v>
+      </c>
+      <c r="F158" t="s">
+        <v>45</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H158" s="2">
+        <v>125</v>
+      </c>
+      <c r="I158" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J158" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A159" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B159" t="s">
+        <v>11</v>
+      </c>
+      <c r="C159" t="s">
+        <v>47</v>
+      </c>
+      <c r="D159" t="s">
+        <v>13</v>
+      </c>
+      <c r="E159" t="s">
+        <v>353</v>
+      </c>
+      <c r="F159" t="s">
+        <v>49</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H159" s="2">
+        <v>38</v>
+      </c>
+      <c r="I159" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J159" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A160" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B160" t="s">
+        <v>11</v>
+      </c>
+      <c r="C160" t="s">
+        <v>51</v>
+      </c>
+      <c r="D160" t="s">
+        <v>13</v>
+      </c>
+      <c r="E160" t="s">
+        <v>355</v>
+      </c>
+      <c r="F160" t="s">
+        <v>53</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H160" s="2">
+        <v>159</v>
+      </c>
+      <c r="I160" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J160" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A161" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B161" t="s">
+        <v>11</v>
+      </c>
+      <c r="C161" t="s">
+        <v>55</v>
+      </c>
+      <c r="D161" t="s">
+        <v>13</v>
+      </c>
+      <c r="E161" t="s">
+        <v>357</v>
+      </c>
+      <c r="F161" t="s">
+        <v>57</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H161" s="2">
+        <v>69</v>
+      </c>
+      <c r="I161" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J161" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A162" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B162" t="s">
+        <v>11</v>
+      </c>
+      <c r="C162" t="s">
+        <v>12</v>
+      </c>
+      <c r="D162" t="s">
+        <v>13</v>
+      </c>
+      <c r="E162" t="s">
+        <v>359</v>
+      </c>
+      <c r="F162" t="s">
+        <v>15</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H162" s="2">
+        <v>52</v>
+      </c>
+      <c r="I162" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J162" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A163" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B163" t="s">
+        <v>11</v>
+      </c>
+      <c r="C163" t="s">
+        <v>20</v>
+      </c>
+      <c r="D163" t="s">
+        <v>13</v>
+      </c>
+      <c r="E163" t="s">
+        <v>361</v>
+      </c>
+      <c r="F163" t="s">
+        <v>22</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H163" s="2">
+        <v>82</v>
+      </c>
+      <c r="I163" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J163" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A164" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B164" t="s">
+        <v>11</v>
+      </c>
+      <c r="C164" t="s">
+        <v>25</v>
+      </c>
+      <c r="D164" t="s">
+        <v>13</v>
+      </c>
+      <c r="E164" t="s">
+        <v>363</v>
+      </c>
+      <c r="F164" t="s">
+        <v>27</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H164" s="2">
+        <v>127</v>
+      </c>
+      <c r="I164" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J164" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A165" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B165" t="s">
+        <v>11</v>
+      </c>
+      <c r="C165" t="s">
+        <v>30</v>
+      </c>
+      <c r="D165" t="s">
+        <v>13</v>
+      </c>
+      <c r="E165" t="s">
+        <v>365</v>
+      </c>
+      <c r="F165" t="s">
+        <v>32</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H165" s="2">
+        <v>133</v>
+      </c>
+      <c r="I165" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J165" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A166" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B166" t="s">
+        <v>11</v>
+      </c>
+      <c r="C166" t="s">
+        <v>35</v>
+      </c>
+      <c r="D166" t="s">
+        <v>13</v>
+      </c>
+      <c r="E166" t="s">
+        <v>367</v>
+      </c>
+      <c r="F166" t="s">
+        <v>37</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H166" s="2">
+        <v>138</v>
+      </c>
+      <c r="I166" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J166" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A167" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B167" t="s">
+        <v>11</v>
+      </c>
+      <c r="C167" t="s">
+        <v>39</v>
+      </c>
+      <c r="D167" t="s">
+        <v>13</v>
+      </c>
+      <c r="E167" t="s">
+        <v>369</v>
+      </c>
+      <c r="F167" t="s">
+        <v>41</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H167" s="2">
+        <v>77</v>
+      </c>
+      <c r="I167" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J167" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A168" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B168" t="s">
+        <v>11</v>
+      </c>
+      <c r="C168" t="s">
+        <v>43</v>
+      </c>
+      <c r="D168" t="s">
+        <v>13</v>
+      </c>
+      <c r="E168" t="s">
+        <v>371</v>
+      </c>
+      <c r="F168" t="s">
+        <v>45</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H168" s="2">
+        <v>125</v>
+      </c>
+      <c r="I168" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J168" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A169" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B169" t="s">
+        <v>11</v>
+      </c>
+      <c r="C169" t="s">
+        <v>47</v>
+      </c>
+      <c r="D169" t="s">
+        <v>13</v>
+      </c>
+      <c r="E169" t="s">
+        <v>373</v>
+      </c>
+      <c r="F169" t="s">
+        <v>49</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H169" s="2">
+        <v>96</v>
+      </c>
+      <c r="I169" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J169" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A170" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B170" t="s">
+        <v>11</v>
+      </c>
+      <c r="C170" t="s">
+        <v>51</v>
+      </c>
+      <c r="D170" t="s">
+        <v>13</v>
+      </c>
+      <c r="E170" t="s">
+        <v>375</v>
+      </c>
+      <c r="F170" t="s">
+        <v>53</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H170" s="2">
+        <v>119</v>
+      </c>
+      <c r="I170" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J170" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A171" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B171" t="s">
+        <v>11</v>
+      </c>
+      <c r="C171" t="s">
+        <v>55</v>
+      </c>
+      <c r="D171" t="s">
+        <v>13</v>
+      </c>
+      <c r="E171" t="s">
+        <v>377</v>
+      </c>
+      <c r="F171" t="s">
+        <v>57</v>
+      </c>
+      <c r="G171" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H171" s="2">
+        <v>34</v>
+      </c>
+      <c r="I171" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J171" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A172" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B172" t="s">
+        <v>11</v>
+      </c>
+      <c r="C172" t="s">
+        <v>12</v>
+      </c>
+      <c r="D172" t="s">
+        <v>13</v>
+      </c>
+      <c r="E172" t="s">
+        <v>379</v>
+      </c>
+      <c r="F172" t="s">
+        <v>15</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H172" s="2">
+        <v>61</v>
+      </c>
+      <c r="I172" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J172" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A173" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B173" t="s">
+        <v>11</v>
+      </c>
+      <c r="C173" t="s">
+        <v>20</v>
+      </c>
+      <c r="D173" t="s">
+        <v>13</v>
+      </c>
+      <c r="E173" t="s">
+        <v>381</v>
+      </c>
+      <c r="F173" t="s">
+        <v>22</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H173" s="2">
+        <v>17</v>
+      </c>
+      <c r="I173" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J173" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A174" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B174" t="s">
+        <v>11</v>
+      </c>
+      <c r="C174" t="s">
+        <v>25</v>
+      </c>
+      <c r="D174" t="s">
+        <v>13</v>
+      </c>
+      <c r="E174" t="s">
+        <v>383</v>
+      </c>
+      <c r="F174" t="s">
+        <v>27</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H174" s="2">
+        <v>71</v>
+      </c>
+      <c r="I174" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J174" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A175" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B175" t="s">
+        <v>11</v>
+      </c>
+      <c r="C175" t="s">
+        <v>30</v>
+      </c>
+      <c r="D175" t="s">
+        <v>13</v>
+      </c>
+      <c r="E175" t="s">
+        <v>385</v>
+      </c>
+      <c r="F175" t="s">
+        <v>32</v>
+      </c>
+      <c r="G175" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H175" s="2">
+        <v>123</v>
+      </c>
+      <c r="I175" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J175" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A176" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B176" t="s">
+        <v>11</v>
+      </c>
+      <c r="C176" t="s">
+        <v>35</v>
+      </c>
+      <c r="D176" t="s">
+        <v>13</v>
+      </c>
+      <c r="E176" t="s">
+        <v>387</v>
+      </c>
+      <c r="F176" t="s">
+        <v>37</v>
+      </c>
+      <c r="G176" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H176" s="2">
+        <v>48</v>
+      </c>
+      <c r="I176" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J176" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A177" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B177" t="s">
+        <v>11</v>
+      </c>
+      <c r="C177" t="s">
+        <v>39</v>
+      </c>
+      <c r="D177" t="s">
+        <v>13</v>
+      </c>
+      <c r="E177" t="s">
+        <v>389</v>
+      </c>
+      <c r="F177" t="s">
+        <v>41</v>
+      </c>
+      <c r="G177" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H177" s="2">
+        <v>51</v>
+      </c>
+      <c r="I177" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J177" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A178" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B178" t="s">
+        <v>11</v>
+      </c>
+      <c r="C178" t="s">
+        <v>43</v>
+      </c>
+      <c r="D178" t="s">
+        <v>13</v>
+      </c>
+      <c r="E178" t="s">
+        <v>391</v>
+      </c>
+      <c r="F178" t="s">
+        <v>45</v>
+      </c>
+      <c r="G178" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H178" s="2">
+        <v>117</v>
+      </c>
+      <c r="I178" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J178" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A179" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B179" t="s">
+        <v>11</v>
+      </c>
+      <c r="C179" t="s">
+        <v>47</v>
+      </c>
+      <c r="D179" t="s">
+        <v>13</v>
+      </c>
+      <c r="E179" t="s">
+        <v>393</v>
+      </c>
+      <c r="F179" t="s">
+        <v>49</v>
+      </c>
+      <c r="G179" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H179" s="2">
+        <v>157</v>
+      </c>
+      <c r="I179" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J179" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A180" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B180" t="s">
+        <v>11</v>
+      </c>
+      <c r="C180" t="s">
+        <v>51</v>
+      </c>
+      <c r="D180" t="s">
+        <v>13</v>
+      </c>
+      <c r="E180" t="s">
+        <v>395</v>
+      </c>
+      <c r="F180" t="s">
+        <v>53</v>
+      </c>
+      <c r="G180" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H180" s="2">
+        <v>150</v>
+      </c>
+      <c r="I180" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J180" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A181" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B181" t="s">
+        <v>11</v>
+      </c>
+      <c r="C181" t="s">
+        <v>55</v>
+      </c>
+      <c r="D181" t="s">
+        <v>13</v>
+      </c>
+      <c r="E181" t="s">
+        <v>397</v>
+      </c>
+      <c r="F181" t="s">
+        <v>57</v>
+      </c>
+      <c r="G181" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H181" s="2">
+        <v>18</v>
+      </c>
+      <c r="I181" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J181" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A182" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B182" t="s">
+        <v>11</v>
+      </c>
+      <c r="C182" t="s">
+        <v>12</v>
+      </c>
+      <c r="D182" t="s">
+        <v>13</v>
+      </c>
+      <c r="E182" t="s">
+        <v>399</v>
+      </c>
+      <c r="F182" t="s">
+        <v>15</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H182" s="2">
+        <v>87</v>
+      </c>
+      <c r="I182" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J182" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A183" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B183" t="s">
+        <v>11</v>
+      </c>
+      <c r="C183" t="s">
+        <v>20</v>
+      </c>
+      <c r="D183" t="s">
+        <v>13</v>
+      </c>
+      <c r="E183" t="s">
+        <v>401</v>
+      </c>
+      <c r="F183" t="s">
+        <v>22</v>
+      </c>
+      <c r="G183" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H183" s="2">
+        <v>119</v>
+      </c>
+      <c r="I183" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J183" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A184" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B184" t="s">
+        <v>11</v>
+      </c>
+      <c r="C184" t="s">
+        <v>25</v>
+      </c>
+      <c r="D184" t="s">
+        <v>13</v>
+      </c>
+      <c r="E184" t="s">
+        <v>403</v>
+      </c>
+      <c r="F184" t="s">
+        <v>27</v>
+      </c>
+      <c r="G184" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H184" s="2">
+        <v>18</v>
+      </c>
+      <c r="I184" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J184" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A185" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B185" t="s">
+        <v>11</v>
+      </c>
+      <c r="C185" t="s">
+        <v>30</v>
+      </c>
+      <c r="D185" t="s">
+        <v>13</v>
+      </c>
+      <c r="E185" t="s">
+        <v>405</v>
+      </c>
+      <c r="F185" t="s">
+        <v>32</v>
+      </c>
+      <c r="G185" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H185" s="2">
+        <v>69</v>
+      </c>
+      <c r="I185" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J185" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A186" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B186" t="s">
+        <v>11</v>
+      </c>
+      <c r="C186" t="s">
+        <v>35</v>
+      </c>
+      <c r="D186" t="s">
+        <v>13</v>
+      </c>
+      <c r="E186" t="s">
+        <v>407</v>
+      </c>
+      <c r="F186" t="s">
+        <v>37</v>
+      </c>
+      <c r="G186" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H186" s="2">
+        <v>62</v>
+      </c>
+      <c r="I186" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J186" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A187" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B187" t="s">
+        <v>11</v>
+      </c>
+      <c r="C187" t="s">
+        <v>39</v>
+      </c>
+      <c r="D187" t="s">
+        <v>13</v>
+      </c>
+      <c r="E187" t="s">
+        <v>409</v>
+      </c>
+      <c r="F187" t="s">
+        <v>41</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H187" s="2">
+        <v>119</v>
+      </c>
+      <c r="I187" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J187" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A188" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B188" t="s">
+        <v>11</v>
+      </c>
+      <c r="C188" t="s">
+        <v>43</v>
+      </c>
+      <c r="D188" t="s">
+        <v>13</v>
+      </c>
+      <c r="E188" t="s">
+        <v>411</v>
+      </c>
+      <c r="F188" t="s">
+        <v>45</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H188" s="2">
+        <v>126</v>
+      </c>
+      <c r="I188" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J188" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A189" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B189" t="s">
+        <v>11</v>
+      </c>
+      <c r="C189" t="s">
+        <v>47</v>
+      </c>
+      <c r="D189" t="s">
+        <v>13</v>
+      </c>
+      <c r="E189" t="s">
+        <v>413</v>
+      </c>
+      <c r="F189" t="s">
+        <v>49</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H189" s="2">
+        <v>157</v>
+      </c>
+      <c r="I189" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J189" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A190" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B190" t="s">
+        <v>11</v>
+      </c>
+      <c r="C190" t="s">
+        <v>51</v>
+      </c>
+      <c r="D190" t="s">
+        <v>13</v>
+      </c>
+      <c r="E190" t="s">
+        <v>415</v>
+      </c>
+      <c r="F190" t="s">
+        <v>53</v>
+      </c>
+      <c r="G190" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H190" s="2">
+        <v>160</v>
+      </c>
+      <c r="I190" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J190" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A191" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B191" t="s">
+        <v>11</v>
+      </c>
+      <c r="C191" t="s">
+        <v>55</v>
+      </c>
+      <c r="D191" t="s">
+        <v>13</v>
+      </c>
+      <c r="E191" t="s">
+        <v>417</v>
+      </c>
+      <c r="F191" t="s">
+        <v>57</v>
+      </c>
+      <c r="G191" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H191" s="2">
+        <v>18</v>
+      </c>
+      <c r="I191" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J191" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A192" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B192" t="s">
+        <v>11</v>
+      </c>
+      <c r="C192" t="s">
+        <v>12</v>
+      </c>
+      <c r="D192" t="s">
+        <v>13</v>
+      </c>
+      <c r="E192" t="s">
+        <v>419</v>
+      </c>
+      <c r="F192" t="s">
+        <v>15</v>
+      </c>
+      <c r="G192" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H192" s="2">
+        <v>113</v>
+      </c>
+      <c r="I192" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J192" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A193" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B193" t="s">
+        <v>11</v>
+      </c>
+      <c r="C193" t="s">
+        <v>20</v>
+      </c>
+      <c r="D193" t="s">
+        <v>13</v>
+      </c>
+      <c r="E193" t="s">
+        <v>421</v>
+      </c>
+      <c r="F193" t="s">
+        <v>22</v>
+      </c>
+      <c r="G193" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H193" s="2">
+        <v>135</v>
+      </c>
+      <c r="I193" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J193" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A194" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B194" t="s">
+        <v>11</v>
+      </c>
+      <c r="C194" t="s">
+        <v>25</v>
+      </c>
+      <c r="D194" t="s">
+        <v>13</v>
+      </c>
+      <c r="E194" t="s">
+        <v>423</v>
+      </c>
+      <c r="F194" t="s">
+        <v>27</v>
+      </c>
+      <c r="G194" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H194" s="2">
+        <v>16</v>
+      </c>
+      <c r="I194" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J194" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A195" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B195" t="s">
+        <v>11</v>
+      </c>
+      <c r="C195" t="s">
+        <v>30</v>
+      </c>
+      <c r="D195" t="s">
+        <v>13</v>
+      </c>
+      <c r="E195" t="s">
+        <v>425</v>
+      </c>
+      <c r="F195" t="s">
+        <v>32</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H195" s="2">
+        <v>54</v>
+      </c>
+      <c r="I195" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J195" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A196" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B196" t="s">
+        <v>11</v>
+      </c>
+      <c r="C196" t="s">
+        <v>35</v>
+      </c>
+      <c r="D196" t="s">
+        <v>13</v>
+      </c>
+      <c r="E196" t="s">
+        <v>427</v>
+      </c>
+      <c r="F196" t="s">
+        <v>37</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H196" s="2">
+        <v>28</v>
+      </c>
+      <c r="I196" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J196" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A197" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B197" t="s">
+        <v>11</v>
+      </c>
+      <c r="C197" t="s">
+        <v>39</v>
+      </c>
+      <c r="D197" t="s">
+        <v>13</v>
+      </c>
+      <c r="E197" t="s">
+        <v>429</v>
+      </c>
+      <c r="F197" t="s">
+        <v>41</v>
+      </c>
+      <c r="G197" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H197" s="2">
+        <v>137</v>
+      </c>
+      <c r="I197" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J197" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A198" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B198" t="s">
+        <v>11</v>
+      </c>
+      <c r="C198" t="s">
+        <v>43</v>
+      </c>
+      <c r="D198" t="s">
+        <v>13</v>
+      </c>
+      <c r="E198" t="s">
+        <v>431</v>
+      </c>
+      <c r="F198" t="s">
+        <v>45</v>
+      </c>
+      <c r="G198" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H198" s="2">
+        <v>30</v>
+      </c>
+      <c r="I198" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J198" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A199" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B199" t="s">
+        <v>11</v>
+      </c>
+      <c r="C199" t="s">
+        <v>47</v>
+      </c>
+      <c r="D199" t="s">
+        <v>13</v>
+      </c>
+      <c r="E199" t="s">
+        <v>433</v>
+      </c>
+      <c r="F199" t="s">
+        <v>49</v>
+      </c>
+      <c r="G199" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H199" s="2">
+        <v>21</v>
+      </c>
+      <c r="I199" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J199" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A200" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B200" t="s">
+        <v>11</v>
+      </c>
+      <c r="C200" t="s">
+        <v>51</v>
+      </c>
+      <c r="D200" t="s">
+        <v>13</v>
+      </c>
+      <c r="E200" t="s">
+        <v>435</v>
+      </c>
+      <c r="F200" t="s">
+        <v>53</v>
+      </c>
+      <c r="G200" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H200" s="2">
+        <v>130</v>
+      </c>
+      <c r="I200" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J200" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A201" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B201" t="s">
+        <v>11</v>
+      </c>
+      <c r="C201" t="s">
+        <v>55</v>
+      </c>
+      <c r="D201" t="s">
+        <v>13</v>
+      </c>
+      <c r="E201" t="s">
+        <v>437</v>
+      </c>
+      <c r="F201" t="s">
+        <v>57</v>
+      </c>
+      <c r="G201" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H201" s="2">
+        <v>155</v>
+      </c>
+      <c r="I201" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J201" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A202" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B202" t="s">
+        <v>11</v>
+      </c>
+      <c r="C202" t="s">
+        <v>12</v>
+      </c>
+      <c r="D202" t="s">
+        <v>13</v>
+      </c>
+      <c r="E202" t="s">
+        <v>439</v>
+      </c>
+      <c r="F202" t="s">
+        <v>15</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H202" s="2">
+        <v>151</v>
+      </c>
+      <c r="I202" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J202" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A203" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B203" t="s">
+        <v>11</v>
+      </c>
+      <c r="C203" t="s">
+        <v>20</v>
+      </c>
+      <c r="D203" t="s">
+        <v>13</v>
+      </c>
+      <c r="E203" t="s">
+        <v>441</v>
+      </c>
+      <c r="F203" t="s">
+        <v>22</v>
+      </c>
+      <c r="G203" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H203" s="2">
+        <v>47</v>
+      </c>
+      <c r="I203" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J203" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A204" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B204" t="s">
+        <v>11</v>
+      </c>
+      <c r="C204" t="s">
+        <v>25</v>
+      </c>
+      <c r="D204" t="s">
+        <v>13</v>
+      </c>
+      <c r="E204" t="s">
+        <v>443</v>
+      </c>
+      <c r="F204" t="s">
+        <v>27</v>
+      </c>
+      <c r="G204" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H204" s="2">
+        <v>154</v>
+      </c>
+      <c r="I204" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J204" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A205" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B205" t="s">
+        <v>11</v>
+      </c>
+      <c r="C205" t="s">
+        <v>30</v>
+      </c>
+      <c r="D205" t="s">
+        <v>13</v>
+      </c>
+      <c r="E205" t="s">
+        <v>445</v>
+      </c>
+      <c r="F205" t="s">
+        <v>32</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H205" s="2">
+        <v>38</v>
+      </c>
+      <c r="I205" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J205" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A206" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B206" t="s">
+        <v>11</v>
+      </c>
+      <c r="C206" t="s">
+        <v>35</v>
+      </c>
+      <c r="D206" t="s">
+        <v>13</v>
+      </c>
+      <c r="E206" t="s">
+        <v>447</v>
+      </c>
+      <c r="F206" t="s">
+        <v>37</v>
+      </c>
+      <c r="G206" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H206" s="2">
+        <v>163</v>
+      </c>
+      <c r="I206" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J206" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A207" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B207" t="s">
+        <v>11</v>
+      </c>
+      <c r="C207" t="s">
+        <v>39</v>
+      </c>
+      <c r="D207" t="s">
+        <v>13</v>
+      </c>
+      <c r="E207" t="s">
+        <v>449</v>
+      </c>
+      <c r="F207" t="s">
+        <v>41</v>
+      </c>
+      <c r="G207" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H207" s="2">
+        <v>79</v>
+      </c>
+      <c r="I207" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J207" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A208" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B208" t="s">
+        <v>11</v>
+      </c>
+      <c r="C208" t="s">
+        <v>43</v>
+      </c>
+      <c r="D208" t="s">
+        <v>13</v>
+      </c>
+      <c r="E208" t="s">
+        <v>451</v>
+      </c>
+      <c r="F208" t="s">
+        <v>45</v>
+      </c>
+      <c r="G208" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H208" s="2">
+        <v>120</v>
+      </c>
+      <c r="I208" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J208" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A209" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B209" t="s">
+        <v>11</v>
+      </c>
+      <c r="C209" t="s">
+        <v>47</v>
+      </c>
+      <c r="D209" t="s">
+        <v>13</v>
+      </c>
+      <c r="E209" t="s">
+        <v>453</v>
+      </c>
+      <c r="F209" t="s">
+        <v>49</v>
+      </c>
+      <c r="G209" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H209" s="2">
+        <v>90</v>
+      </c>
+      <c r="I209" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J209" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A210" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B210" t="s">
+        <v>11</v>
+      </c>
+      <c r="C210" t="s">
+        <v>51</v>
+      </c>
+      <c r="D210" t="s">
+        <v>13</v>
+      </c>
+      <c r="E210" t="s">
+        <v>455</v>
+      </c>
+      <c r="F210" t="s">
+        <v>53</v>
+      </c>
+      <c r="G210" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H210" s="2">
+        <v>22</v>
+      </c>
+      <c r="I210" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J210" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A211" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B211" t="s">
+        <v>11</v>
+      </c>
+      <c r="C211" t="s">
+        <v>55</v>
+      </c>
+      <c r="D211" t="s">
+        <v>13</v>
+      </c>
+      <c r="E211" t="s">
+        <v>457</v>
+      </c>
+      <c r="F211" t="s">
+        <v>57</v>
+      </c>
+      <c r="G211" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H211" s="2">
+        <v>85</v>
+      </c>
+      <c r="I211" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J211" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A212" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B212" t="s">
+        <v>11</v>
+      </c>
+      <c r="C212" t="s">
+        <v>12</v>
+      </c>
+      <c r="D212" t="s">
+        <v>13</v>
+      </c>
+      <c r="E212" t="s">
+        <v>459</v>
+      </c>
+      <c r="F212" t="s">
+        <v>15</v>
+      </c>
+      <c r="G212" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H212" s="2">
+        <v>124</v>
+      </c>
+      <c r="I212" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J212" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A213" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B213" t="s">
+        <v>11</v>
+      </c>
+      <c r="C213" t="s">
+        <v>20</v>
+      </c>
+      <c r="D213" t="s">
+        <v>13</v>
+      </c>
+      <c r="E213" t="s">
+        <v>461</v>
+      </c>
+      <c r="F213" t="s">
+        <v>22</v>
+      </c>
+      <c r="G213" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H213" s="2">
+        <v>25</v>
+      </c>
+      <c r="I213" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J213" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A214" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B214" t="s">
+        <v>11</v>
+      </c>
+      <c r="C214" t="s">
+        <v>25</v>
+      </c>
+      <c r="D214" t="s">
+        <v>13</v>
+      </c>
+      <c r="E214" t="s">
+        <v>463</v>
+      </c>
+      <c r="F214" t="s">
+        <v>27</v>
+      </c>
+      <c r="G214" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H214" s="2">
+        <v>154</v>
+      </c>
+      <c r="I214" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J214" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A215" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B215" t="s">
+        <v>11</v>
+      </c>
+      <c r="C215" t="s">
+        <v>30</v>
+      </c>
+      <c r="D215" t="s">
+        <v>13</v>
+      </c>
+      <c r="E215" t="s">
+        <v>465</v>
+      </c>
+      <c r="F215" t="s">
+        <v>32</v>
+      </c>
+      <c r="G215" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H215" s="2">
+        <v>62</v>
+      </c>
+      <c r="I215" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J215" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A216" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B216" t="s">
+        <v>11</v>
+      </c>
+      <c r="C216" t="s">
+        <v>35</v>
+      </c>
+      <c r="D216" t="s">
+        <v>13</v>
+      </c>
+      <c r="E216" t="s">
+        <v>467</v>
+      </c>
+      <c r="F216" t="s">
+        <v>37</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H216" s="2">
+        <v>136</v>
+      </c>
+      <c r="I216" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J216" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A217" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B217" t="s">
+        <v>11</v>
+      </c>
+      <c r="C217" t="s">
+        <v>39</v>
+      </c>
+      <c r="D217" t="s">
+        <v>13</v>
+      </c>
+      <c r="E217" t="s">
+        <v>469</v>
+      </c>
+      <c r="F217" t="s">
+        <v>41</v>
+      </c>
+      <c r="G217" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H217" s="2">
+        <v>105</v>
+      </c>
+      <c r="I217" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J217" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A218" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B218" t="s">
+        <v>11</v>
+      </c>
+      <c r="C218" t="s">
+        <v>43</v>
+      </c>
+      <c r="D218" t="s">
+        <v>13</v>
+      </c>
+      <c r="E218" t="s">
+        <v>471</v>
+      </c>
+      <c r="F218" t="s">
+        <v>45</v>
+      </c>
+      <c r="G218" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H218" s="2">
+        <v>19</v>
+      </c>
+      <c r="I218" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J218" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A219" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B219" t="s">
+        <v>11</v>
+      </c>
+      <c r="C219" t="s">
+        <v>47</v>
+      </c>
+      <c r="D219" t="s">
+        <v>13</v>
+      </c>
+      <c r="E219" t="s">
+        <v>473</v>
+      </c>
+      <c r="F219" t="s">
+        <v>49</v>
+      </c>
+      <c r="G219" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H219" s="2">
+        <v>66</v>
+      </c>
+      <c r="I219" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J219" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A220" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B220" t="s">
+        <v>11</v>
+      </c>
+      <c r="C220" t="s">
+        <v>51</v>
+      </c>
+      <c r="D220" t="s">
+        <v>13</v>
+      </c>
+      <c r="E220" t="s">
+        <v>475</v>
+      </c>
+      <c r="F220" t="s">
+        <v>53</v>
+      </c>
+      <c r="G220" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H220" s="2">
+        <v>82</v>
+      </c>
+      <c r="I220" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J220" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A221" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B221" t="s">
+        <v>11</v>
+      </c>
+      <c r="C221" t="s">
+        <v>55</v>
+      </c>
+      <c r="D221" t="s">
+        <v>13</v>
+      </c>
+      <c r="E221" t="s">
+        <v>477</v>
+      </c>
+      <c r="F221" t="s">
+        <v>57</v>
+      </c>
+      <c r="G221" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H221" s="2">
+        <v>40</v>
+      </c>
+      <c r="I221" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J221" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A222" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B222" t="s">
+        <v>11</v>
+      </c>
+      <c r="C222" t="s">
+        <v>12</v>
+      </c>
+      <c r="D222" t="s">
+        <v>13</v>
+      </c>
+      <c r="E222" t="s">
+        <v>479</v>
+      </c>
+      <c r="F222" t="s">
+        <v>15</v>
+      </c>
+      <c r="G222" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H222" s="2">
+        <v>108</v>
+      </c>
+      <c r="I222" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J222" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A223" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="B223" t="s">
+        <v>11</v>
+      </c>
+      <c r="C223" t="s">
+        <v>20</v>
+      </c>
+      <c r="D223" t="s">
+        <v>13</v>
+      </c>
+      <c r="E223" t="s">
+        <v>481</v>
+      </c>
+      <c r="F223" t="s">
+        <v>22</v>
+      </c>
+      <c r="G223" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H223" s="2">
+        <v>18</v>
+      </c>
+      <c r="I223" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J223" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A224" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B224" t="s">
+        <v>11</v>
+      </c>
+      <c r="C224" t="s">
+        <v>25</v>
+      </c>
+      <c r="D224" t="s">
+        <v>13</v>
+      </c>
+      <c r="E224" t="s">
+        <v>483</v>
+      </c>
+      <c r="F224" t="s">
+        <v>27</v>
+      </c>
+      <c r="G224" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H224" s="2">
+        <v>128</v>
+      </c>
+      <c r="I224" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J224" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A225" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B225" t="s">
+        <v>11</v>
+      </c>
+      <c r="C225" t="s">
+        <v>30</v>
+      </c>
+      <c r="D225" t="s">
+        <v>13</v>
+      </c>
+      <c r="E225" t="s">
+        <v>485</v>
+      </c>
+      <c r="F225" t="s">
+        <v>32</v>
+      </c>
+      <c r="G225" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H225" s="2">
+        <v>123</v>
+      </c>
+      <c r="I225" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J225" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A226" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B226" t="s">
+        <v>11</v>
+      </c>
+      <c r="C226" t="s">
+        <v>35</v>
+      </c>
+      <c r="D226" t="s">
+        <v>13</v>
+      </c>
+      <c r="E226" t="s">
+        <v>487</v>
+      </c>
+      <c r="F226" t="s">
+        <v>37</v>
+      </c>
+      <c r="G226" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H226" s="2">
+        <v>53</v>
+      </c>
+      <c r="I226" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J226" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A227" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B227" t="s">
+        <v>11</v>
+      </c>
+      <c r="C227" t="s">
+        <v>39</v>
+      </c>
+      <c r="D227" t="s">
+        <v>13</v>
+      </c>
+      <c r="E227" t="s">
+        <v>489</v>
+      </c>
+      <c r="F227" t="s">
+        <v>41</v>
+      </c>
+      <c r="G227" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H227" s="2">
+        <v>146</v>
+      </c>
+      <c r="I227" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J227" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A228" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B228" t="s">
+        <v>11</v>
+      </c>
+      <c r="C228" t="s">
+        <v>43</v>
+      </c>
+      <c r="D228" t="s">
+        <v>13</v>
+      </c>
+      <c r="E228" t="s">
+        <v>491</v>
+      </c>
+      <c r="F228" t="s">
+        <v>45</v>
+      </c>
+      <c r="G228" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H228" s="2">
+        <v>109</v>
+      </c>
+      <c r="I228" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J228" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A229" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B229" t="s">
+        <v>11</v>
+      </c>
+      <c r="C229" t="s">
+        <v>47</v>
+      </c>
+      <c r="D229" t="s">
+        <v>13</v>
+      </c>
+      <c r="E229" t="s">
+        <v>493</v>
+      </c>
+      <c r="F229" t="s">
+        <v>49</v>
+      </c>
+      <c r="G229" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H229" s="2">
+        <v>106</v>
+      </c>
+      <c r="I229" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J229" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A230" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B230" t="s">
+        <v>11</v>
+      </c>
+      <c r="C230" t="s">
+        <v>51</v>
+      </c>
+      <c r="D230" t="s">
+        <v>13</v>
+      </c>
+      <c r="E230" t="s">
+        <v>495</v>
+      </c>
+      <c r="F230" t="s">
+        <v>53</v>
+      </c>
+      <c r="G230" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H230" s="2">
+        <v>92</v>
+      </c>
+      <c r="I230" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J230" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A231" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B231" t="s">
+        <v>11</v>
+      </c>
+      <c r="C231" t="s">
+        <v>55</v>
+      </c>
+      <c r="D231" t="s">
+        <v>13</v>
+      </c>
+      <c r="E231" t="s">
+        <v>497</v>
+      </c>
+      <c r="F231" t="s">
+        <v>57</v>
+      </c>
+      <c r="G231" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H231" s="2">
+        <v>146</v>
+      </c>
+      <c r="I231" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J231" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A232" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B232" t="s">
+        <v>11</v>
+      </c>
+      <c r="C232" t="s">
+        <v>12</v>
+      </c>
+      <c r="D232" t="s">
+        <v>13</v>
+      </c>
+      <c r="E232" t="s">
+        <v>499</v>
+      </c>
+      <c r="F232" t="s">
+        <v>15</v>
+      </c>
+      <c r="G232" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H232" s="2">
+        <v>83</v>
+      </c>
+      <c r="I232" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J232" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A233" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B233" t="s">
+        <v>11</v>
+      </c>
+      <c r="C233" t="s">
+        <v>20</v>
+      </c>
+      <c r="D233" t="s">
+        <v>13</v>
+      </c>
+      <c r="E233" t="s">
+        <v>501</v>
+      </c>
+      <c r="F233" t="s">
+        <v>22</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H233" s="2">
+        <v>138</v>
+      </c>
+      <c r="I233" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J233" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A234" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B234" t="s">
+        <v>11</v>
+      </c>
+      <c r="C234" t="s">
+        <v>25</v>
+      </c>
+      <c r="D234" t="s">
+        <v>13</v>
+      </c>
+      <c r="E234" t="s">
+        <v>503</v>
+      </c>
+      <c r="F234" t="s">
+        <v>27</v>
+      </c>
+      <c r="G234" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H234" s="2">
+        <v>118</v>
+      </c>
+      <c r="I234" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J234" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A235" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B235" t="s">
+        <v>11</v>
+      </c>
+      <c r="C235" t="s">
+        <v>30</v>
+      </c>
+      <c r="D235" t="s">
+        <v>13</v>
+      </c>
+      <c r="E235" t="s">
+        <v>505</v>
+      </c>
+      <c r="F235" t="s">
+        <v>32</v>
+      </c>
+      <c r="G235" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H235" s="2">
+        <v>89</v>
+      </c>
+      <c r="I235" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J235" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A236" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B236" t="s">
+        <v>11</v>
+      </c>
+      <c r="C236" t="s">
+        <v>35</v>
+      </c>
+      <c r="D236" t="s">
+        <v>13</v>
+      </c>
+      <c r="E236" t="s">
+        <v>507</v>
+      </c>
+      <c r="F236" t="s">
+        <v>37</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H236" s="2">
+        <v>94</v>
+      </c>
+      <c r="I236" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J236" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A237" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B237" t="s">
+        <v>11</v>
+      </c>
+      <c r="C237" t="s">
+        <v>39</v>
+      </c>
+      <c r="D237" t="s">
+        <v>13</v>
+      </c>
+      <c r="E237" t="s">
+        <v>509</v>
+      </c>
+      <c r="F237" t="s">
+        <v>41</v>
+      </c>
+      <c r="G237" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H237" s="2">
+        <v>58</v>
+      </c>
+      <c r="I237" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J237" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A238" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B238" t="s">
+        <v>11</v>
+      </c>
+      <c r="C238" t="s">
+        <v>43</v>
+      </c>
+      <c r="D238" t="s">
+        <v>13</v>
+      </c>
+      <c r="E238" t="s">
+        <v>511</v>
+      </c>
+      <c r="F238" t="s">
+        <v>45</v>
+      </c>
+      <c r="G238" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H238" s="2">
+        <v>73</v>
+      </c>
+      <c r="I238" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J238" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A239" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="B239" t="s">
+        <v>11</v>
+      </c>
+      <c r="C239" t="s">
+        <v>47</v>
+      </c>
+      <c r="D239" t="s">
+        <v>13</v>
+      </c>
+      <c r="E239" t="s">
+        <v>513</v>
+      </c>
+      <c r="F239" t="s">
+        <v>49</v>
+      </c>
+      <c r="G239" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H239" s="2">
+        <v>87</v>
+      </c>
+      <c r="I239" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J239" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A240" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="B240" t="s">
+        <v>11</v>
+      </c>
+      <c r="C240" t="s">
+        <v>51</v>
+      </c>
+      <c r="D240" t="s">
+        <v>13</v>
+      </c>
+      <c r="E240" t="s">
+        <v>515</v>
+      </c>
+      <c r="F240" t="s">
+        <v>53</v>
+      </c>
+      <c r="G240" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H240" s="2">
+        <v>81</v>
+      </c>
+      <c r="I240" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J240" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A241" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B241" t="s">
+        <v>11</v>
+      </c>
+      <c r="C241" t="s">
+        <v>55</v>
+      </c>
+      <c r="D241" t="s">
+        <v>13</v>
+      </c>
+      <c r="E241" t="s">
+        <v>517</v>
+      </c>
+      <c r="F241" t="s">
+        <v>57</v>
+      </c>
+      <c r="G241" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H241" s="2">
+        <v>37</v>
+      </c>
+      <c r="I241" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J241" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A242" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B242" t="s">
+        <v>11</v>
+      </c>
+      <c r="C242" t="s">
+        <v>12</v>
+      </c>
+      <c r="D242" t="s">
+        <v>13</v>
+      </c>
+      <c r="E242" t="s">
+        <v>519</v>
+      </c>
+      <c r="F242" t="s">
+        <v>15</v>
+      </c>
+      <c r="G242" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H242" s="2">
+        <v>29</v>
+      </c>
+      <c r="I242" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J242" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A243" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B243" t="s">
+        <v>11</v>
+      </c>
+      <c r="C243" t="s">
+        <v>20</v>
+      </c>
+      <c r="D243" t="s">
+        <v>13</v>
+      </c>
+      <c r="E243" t="s">
+        <v>521</v>
+      </c>
+      <c r="F243" t="s">
+        <v>22</v>
+      </c>
+      <c r="G243" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H243" s="2">
+        <v>107</v>
+      </c>
+      <c r="I243" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J243" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A244" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B244" t="s">
+        <v>11</v>
+      </c>
+      <c r="C244" t="s">
+        <v>25</v>
+      </c>
+      <c r="D244" t="s">
+        <v>13</v>
+      </c>
+      <c r="E244" t="s">
+        <v>523</v>
+      </c>
+      <c r="F244" t="s">
+        <v>27</v>
+      </c>
+      <c r="G244" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H244" s="2">
+        <v>48</v>
+      </c>
+      <c r="I244" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J244" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A245" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="B245" t="s">
+        <v>11</v>
+      </c>
+      <c r="C245" t="s">
+        <v>30</v>
+      </c>
+      <c r="D245" t="s">
+        <v>13</v>
+      </c>
+      <c r="E245" t="s">
+        <v>525</v>
+      </c>
+      <c r="F245" t="s">
+        <v>32</v>
+      </c>
+      <c r="G245" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H245" s="2">
+        <v>48</v>
+      </c>
+      <c r="I245" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J245" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A246" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="B246" t="s">
+        <v>11</v>
+      </c>
+      <c r="C246" t="s">
+        <v>35</v>
+      </c>
+      <c r="D246" t="s">
+        <v>13</v>
+      </c>
+      <c r="E246" t="s">
+        <v>527</v>
+      </c>
+      <c r="F246" t="s">
+        <v>37</v>
+      </c>
+      <c r="G246" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H246" s="2">
+        <v>74</v>
+      </c>
+      <c r="I246" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J246" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A247" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B247" t="s">
+        <v>11</v>
+      </c>
+      <c r="C247" t="s">
+        <v>39</v>
+      </c>
+      <c r="D247" t="s">
+        <v>13</v>
+      </c>
+      <c r="E247" t="s">
+        <v>529</v>
+      </c>
+      <c r="F247" t="s">
+        <v>41</v>
+      </c>
+      <c r="G247" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H247" s="2">
+        <v>52</v>
+      </c>
+      <c r="I247" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J247" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A248" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B248" t="s">
+        <v>11</v>
+      </c>
+      <c r="C248" t="s">
+        <v>43</v>
+      </c>
+      <c r="D248" t="s">
+        <v>13</v>
+      </c>
+      <c r="E248" t="s">
+        <v>531</v>
+      </c>
+      <c r="F248" t="s">
+        <v>45</v>
+      </c>
+      <c r="G248" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H248" s="2">
+        <v>34</v>
+      </c>
+      <c r="I248" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J248" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A249" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="B249" t="s">
+        <v>11</v>
+      </c>
+      <c r="C249" t="s">
+        <v>47</v>
+      </c>
+      <c r="D249" t="s">
+        <v>13</v>
+      </c>
+      <c r="E249" t="s">
+        <v>533</v>
+      </c>
+      <c r="F249" t="s">
+        <v>49</v>
+      </c>
+      <c r="G249" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H249" s="2">
+        <v>148</v>
+      </c>
+      <c r="I249" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J249" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A250" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B250" t="s">
+        <v>11</v>
+      </c>
+      <c r="C250" t="s">
+        <v>51</v>
+      </c>
+      <c r="D250" t="s">
+        <v>13</v>
+      </c>
+      <c r="E250" t="s">
+        <v>535</v>
+      </c>
+      <c r="F250" t="s">
+        <v>53</v>
+      </c>
+      <c r="G250" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H250" s="2">
+        <v>160</v>
+      </c>
+      <c r="I250" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J250" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A251" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="B251" t="s">
+        <v>11</v>
+      </c>
+      <c r="C251" t="s">
+        <v>55</v>
+      </c>
+      <c r="D251" t="s">
+        <v>13</v>
+      </c>
+      <c r="E251" t="s">
+        <v>537</v>
+      </c>
+      <c r="F251" t="s">
+        <v>57</v>
+      </c>
+      <c r="G251" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H251" s="2">
+        <v>15</v>
+      </c>
+      <c r="I251" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J251" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A252" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="B252" t="s">
+        <v>11</v>
+      </c>
+      <c r="C252" t="s">
+        <v>12</v>
+      </c>
+      <c r="D252" t="s">
+        <v>13</v>
+      </c>
+      <c r="E252" t="s">
+        <v>539</v>
+      </c>
+      <c r="F252" t="s">
+        <v>15</v>
+      </c>
+      <c r="G252" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H252" s="2">
+        <v>101</v>
+      </c>
+      <c r="I252" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J252" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A253" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="B253" t="s">
+        <v>11</v>
+      </c>
+      <c r="C253" t="s">
+        <v>20</v>
+      </c>
+      <c r="D253" t="s">
+        <v>13</v>
+      </c>
+      <c r="E253" t="s">
+        <v>541</v>
+      </c>
+      <c r="F253" t="s">
+        <v>22</v>
+      </c>
+      <c r="G253" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H253" s="2">
+        <v>154</v>
+      </c>
+      <c r="I253" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J253" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A254" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="B254" t="s">
+        <v>11</v>
+      </c>
+      <c r="C254" t="s">
+        <v>25</v>
+      </c>
+      <c r="D254" t="s">
+        <v>13</v>
+      </c>
+      <c r="E254" t="s">
+        <v>543</v>
+      </c>
+      <c r="F254" t="s">
+        <v>27</v>
+      </c>
+      <c r="G254" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H254" s="2">
+        <v>35</v>
+      </c>
+      <c r="I254" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J254" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A255" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="B255" t="s">
+        <v>11</v>
+      </c>
+      <c r="C255" t="s">
+        <v>30</v>
+      </c>
+      <c r="D255" t="s">
+        <v>13</v>
+      </c>
+      <c r="E255" t="s">
+        <v>545</v>
+      </c>
+      <c r="F255" t="s">
+        <v>32</v>
+      </c>
+      <c r="G255" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H255" s="2">
+        <v>30</v>
+      </c>
+      <c r="I255" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J255" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A256" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B256" t="s">
+        <v>11</v>
+      </c>
+      <c r="C256" t="s">
+        <v>35</v>
+      </c>
+      <c r="D256" t="s">
+        <v>13</v>
+      </c>
+      <c r="E256" t="s">
+        <v>547</v>
+      </c>
+      <c r="F256" t="s">
+        <v>37</v>
+      </c>
+      <c r="G256" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H256" s="2">
+        <v>142</v>
+      </c>
+      <c r="I256" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J256" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A257" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B257" t="s">
+        <v>11</v>
+      </c>
+      <c r="C257" t="s">
+        <v>39</v>
+      </c>
+      <c r="D257" t="s">
+        <v>13</v>
+      </c>
+      <c r="E257" t="s">
+        <v>549</v>
+      </c>
+      <c r="F257" t="s">
+        <v>41</v>
+      </c>
+      <c r="G257" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H257" s="2">
+        <v>113</v>
+      </c>
+      <c r="I257" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J257" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A258" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="B258" t="s">
+        <v>11</v>
+      </c>
+      <c r="C258" t="s">
+        <v>43</v>
+      </c>
+      <c r="D258" t="s">
+        <v>13</v>
+      </c>
+      <c r="E258" t="s">
+        <v>551</v>
+      </c>
+      <c r="F258" t="s">
+        <v>45</v>
+      </c>
+      <c r="G258" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H258" s="2">
+        <v>43</v>
+      </c>
+      <c r="I258" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J258" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A259" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B259" t="s">
+        <v>11</v>
+      </c>
+      <c r="C259" t="s">
+        <v>47</v>
+      </c>
+      <c r="D259" t="s">
+        <v>13</v>
+      </c>
+      <c r="E259" t="s">
+        <v>553</v>
+      </c>
+      <c r="F259" t="s">
+        <v>49</v>
+      </c>
+      <c r="G259" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H259" s="2">
+        <v>43</v>
+      </c>
+      <c r="I259" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J259" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A260" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B260" t="s">
+        <v>11</v>
+      </c>
+      <c r="C260" t="s">
+        <v>51</v>
+      </c>
+      <c r="D260" t="s">
+        <v>13</v>
+      </c>
+      <c r="E260" t="s">
+        <v>555</v>
+      </c>
+      <c r="F260" t="s">
+        <v>53</v>
+      </c>
+      <c r="G260" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H260" s="2">
+        <v>93</v>
+      </c>
+      <c r="I260" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J260" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A261" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B261" t="s">
+        <v>11</v>
+      </c>
+      <c r="C261" t="s">
+        <v>55</v>
+      </c>
+      <c r="D261" t="s">
+        <v>13</v>
+      </c>
+      <c r="E261" t="s">
+        <v>557</v>
+      </c>
+      <c r="F261" t="s">
+        <v>57</v>
+      </c>
+      <c r="G261" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H261" s="2">
+        <v>140</v>
+      </c>
+      <c r="I261" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J261" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A262" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="B262" t="s">
+        <v>11</v>
+      </c>
+      <c r="C262" t="s">
+        <v>12</v>
+      </c>
+      <c r="D262" t="s">
+        <v>13</v>
+      </c>
+      <c r="E262" t="s">
+        <v>559</v>
+      </c>
+      <c r="F262" t="s">
+        <v>15</v>
+      </c>
+      <c r="G262" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H262" s="2">
+        <v>113</v>
+      </c>
+      <c r="I262" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J262" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A263" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="B263" t="s">
+        <v>11</v>
+      </c>
+      <c r="C263" t="s">
+        <v>20</v>
+      </c>
+      <c r="D263" t="s">
+        <v>13</v>
+      </c>
+      <c r="E263" t="s">
+        <v>561</v>
+      </c>
+      <c r="F263" t="s">
+        <v>22</v>
+      </c>
+      <c r="G263" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H263" s="2">
+        <v>120</v>
+      </c>
+      <c r="I263" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J263" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A264" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B264" t="s">
+        <v>11</v>
+      </c>
+      <c r="C264" t="s">
+        <v>25</v>
+      </c>
+      <c r="D264" t="s">
+        <v>13</v>
+      </c>
+      <c r="E264" t="s">
+        <v>563</v>
+      </c>
+      <c r="F264" t="s">
+        <v>27</v>
+      </c>
+      <c r="G264" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H264" s="2">
+        <v>113</v>
+      </c>
+      <c r="I264" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J264" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A265" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B265" t="s">
+        <v>11</v>
+      </c>
+      <c r="C265" t="s">
+        <v>30</v>
+      </c>
+      <c r="D265" t="s">
+        <v>13</v>
+      </c>
+      <c r="E265" t="s">
+        <v>565</v>
+      </c>
+      <c r="F265" t="s">
+        <v>32</v>
+      </c>
+      <c r="G265" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H265" s="2">
+        <v>100</v>
+      </c>
+      <c r="I265" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J265" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A266" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B266" t="s">
+        <v>11</v>
+      </c>
+      <c r="C266" t="s">
+        <v>35</v>
+      </c>
+      <c r="D266" t="s">
+        <v>13</v>
+      </c>
+      <c r="E266" t="s">
+        <v>567</v>
+      </c>
+      <c r="F266" t="s">
+        <v>37</v>
+      </c>
+      <c r="G266" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H266" s="2">
+        <v>133</v>
+      </c>
+      <c r="I266" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J266" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A267" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="B267" t="s">
+        <v>11</v>
+      </c>
+      <c r="C267" t="s">
+        <v>39</v>
+      </c>
+      <c r="D267" t="s">
+        <v>13</v>
+      </c>
+      <c r="E267" t="s">
+        <v>569</v>
+      </c>
+      <c r="F267" t="s">
+        <v>41</v>
+      </c>
+      <c r="G267" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H267" s="2">
+        <v>65</v>
+      </c>
+      <c r="I267" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J267" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A268" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B268" t="s">
+        <v>11</v>
+      </c>
+      <c r="C268" t="s">
+        <v>43</v>
+      </c>
+      <c r="D268" t="s">
+        <v>13</v>
+      </c>
+      <c r="E268" t="s">
+        <v>571</v>
+      </c>
+      <c r="F268" t="s">
+        <v>45</v>
+      </c>
+      <c r="G268" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H268" s="2">
+        <v>71</v>
+      </c>
+      <c r="I268" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J268" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A269" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B269" t="s">
+        <v>11</v>
+      </c>
+      <c r="C269" t="s">
+        <v>47</v>
+      </c>
+      <c r="D269" t="s">
+        <v>13</v>
+      </c>
+      <c r="E269" t="s">
+        <v>573</v>
+      </c>
+      <c r="F269" t="s">
+        <v>49</v>
+      </c>
+      <c r="G269" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H269" s="2">
+        <v>78</v>
+      </c>
+      <c r="I269" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J269" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A270" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="B270" t="s">
+        <v>11</v>
+      </c>
+      <c r="C270" t="s">
+        <v>51</v>
+      </c>
+      <c r="D270" t="s">
+        <v>13</v>
+      </c>
+      <c r="E270" t="s">
+        <v>575</v>
+      </c>
+      <c r="F270" t="s">
+        <v>53</v>
+      </c>
+      <c r="G270" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H270" s="2">
+        <v>125</v>
+      </c>
+      <c r="I270" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J270" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A271" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="B271" t="s">
+        <v>11</v>
+      </c>
+      <c r="C271" t="s">
+        <v>55</v>
+      </c>
+      <c r="D271" t="s">
+        <v>13</v>
+      </c>
+      <c r="E271" t="s">
+        <v>577</v>
+      </c>
+      <c r="F271" t="s">
+        <v>57</v>
+      </c>
+      <c r="G271" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H271" s="2">
+        <v>70</v>
+      </c>
+      <c r="I271" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J271" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A272" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B272" t="s">
+        <v>11</v>
+      </c>
+      <c r="C272" t="s">
+        <v>12</v>
+      </c>
+      <c r="D272" t="s">
+        <v>13</v>
+      </c>
+      <c r="E272" t="s">
+        <v>579</v>
+      </c>
+      <c r="F272" t="s">
+        <v>15</v>
+      </c>
+      <c r="G272" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H272" s="2">
+        <v>99</v>
+      </c>
+      <c r="I272" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J272" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A273" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B273" t="s">
+        <v>11</v>
+      </c>
+      <c r="C273" t="s">
+        <v>20</v>
+      </c>
+      <c r="D273" t="s">
+        <v>13</v>
+      </c>
+      <c r="E273" t="s">
+        <v>581</v>
+      </c>
+      <c r="F273" t="s">
+        <v>22</v>
+      </c>
+      <c r="G273" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H273" s="2">
+        <v>40</v>
+      </c>
+      <c r="I273" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J273" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A274" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B274" t="s">
+        <v>11</v>
+      </c>
+      <c r="C274" t="s">
+        <v>25</v>
+      </c>
+      <c r="D274" t="s">
+        <v>13</v>
+      </c>
+      <c r="E274" t="s">
+        <v>583</v>
+      </c>
+      <c r="F274" t="s">
+        <v>27</v>
+      </c>
+      <c r="G274" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H274" s="2">
+        <v>114</v>
+      </c>
+      <c r="I274" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J274" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A275" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B275" t="s">
+        <v>11</v>
+      </c>
+      <c r="C275" t="s">
+        <v>30</v>
+      </c>
+      <c r="D275" t="s">
+        <v>13</v>
+      </c>
+      <c r="E275" t="s">
+        <v>585</v>
+      </c>
+      <c r="F275" t="s">
+        <v>32</v>
+      </c>
+      <c r="G275" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H275" s="2">
+        <v>109</v>
+      </c>
+      <c r="I275" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J275" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A276" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="B276" t="s">
+        <v>11</v>
+      </c>
+      <c r="C276" t="s">
+        <v>35</v>
+      </c>
+      <c r="D276" t="s">
+        <v>13</v>
+      </c>
+      <c r="E276" t="s">
+        <v>587</v>
+      </c>
+      <c r="F276" t="s">
+        <v>37</v>
+      </c>
+      <c r="G276" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H276" s="2">
+        <v>128</v>
+      </c>
+      <c r="I276" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J276" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A277" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="B277" t="s">
+        <v>11</v>
+      </c>
+      <c r="C277" t="s">
+        <v>39</v>
+      </c>
+      <c r="D277" t="s">
+        <v>13</v>
+      </c>
+      <c r="E277" t="s">
+        <v>589</v>
+      </c>
+      <c r="F277" t="s">
+        <v>41</v>
+      </c>
+      <c r="G277" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H277" s="2">
+        <v>145</v>
+      </c>
+      <c r="I277" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J277" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A278" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B278" t="s">
+        <v>11</v>
+      </c>
+      <c r="C278" t="s">
+        <v>43</v>
+      </c>
+      <c r="D278" t="s">
+        <v>13</v>
+      </c>
+      <c r="E278" t="s">
+        <v>591</v>
+      </c>
+      <c r="F278" t="s">
+        <v>45</v>
+      </c>
+      <c r="G278" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H278" s="2">
+        <v>59</v>
+      </c>
+      <c r="I278" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J278" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A279" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B279" t="s">
+        <v>11</v>
+      </c>
+      <c r="C279" t="s">
+        <v>47</v>
+      </c>
+      <c r="D279" t="s">
+        <v>13</v>
+      </c>
+      <c r="E279" t="s">
+        <v>593</v>
+      </c>
+      <c r="F279" t="s">
+        <v>49</v>
+      </c>
+      <c r="G279" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H279" s="2">
+        <v>157</v>
+      </c>
+      <c r="I279" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J279" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A280" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B280" t="s">
+        <v>11</v>
+      </c>
+      <c r="C280" t="s">
+        <v>51</v>
+      </c>
+      <c r="D280" t="s">
+        <v>13</v>
+      </c>
+      <c r="E280" t="s">
+        <v>595</v>
+      </c>
+      <c r="F280" t="s">
+        <v>53</v>
+      </c>
+      <c r="G280" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H280" s="2">
+        <v>132</v>
+      </c>
+      <c r="I280" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J280" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A281" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B281" t="s">
+        <v>11</v>
+      </c>
+      <c r="C281" t="s">
+        <v>55</v>
+      </c>
+      <c r="D281" t="s">
+        <v>13</v>
+      </c>
+      <c r="E281" t="s">
+        <v>597</v>
+      </c>
+      <c r="F281" t="s">
+        <v>57</v>
+      </c>
+      <c r="G281" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H281" s="2">
+        <v>128</v>
+      </c>
+      <c r="I281" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J281" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A282" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B282" t="s">
+        <v>11</v>
+      </c>
+      <c r="C282" t="s">
+        <v>12</v>
+      </c>
+      <c r="D282" t="s">
+        <v>13</v>
+      </c>
+      <c r="E282" t="s">
+        <v>599</v>
+      </c>
+      <c r="F282" t="s">
+        <v>15</v>
+      </c>
+      <c r="G282" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H282" s="2">
+        <v>108</v>
+      </c>
+      <c r="I282" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J282" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A283" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="B283" t="s">
+        <v>11</v>
+      </c>
+      <c r="C283" t="s">
+        <v>20</v>
+      </c>
+      <c r="D283" t="s">
+        <v>13</v>
+      </c>
+      <c r="E283" t="s">
+        <v>601</v>
+      </c>
+      <c r="F283" t="s">
+        <v>22</v>
+      </c>
+      <c r="G283" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H283" s="2">
+        <v>62</v>
+      </c>
+      <c r="I283" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J283" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A284" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B284" t="s">
+        <v>11</v>
+      </c>
+      <c r="C284" t="s">
+        <v>25</v>
+      </c>
+      <c r="D284" t="s">
+        <v>13</v>
+      </c>
+      <c r="E284" t="s">
+        <v>603</v>
+      </c>
+      <c r="F284" t="s">
+        <v>27</v>
+      </c>
+      <c r="G284" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H284" s="2">
+        <v>44</v>
+      </c>
+      <c r="I284" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J284" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A285" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="B285" t="s">
+        <v>11</v>
+      </c>
+      <c r="C285" t="s">
+        <v>30</v>
+      </c>
+      <c r="D285" t="s">
+        <v>13</v>
+      </c>
+      <c r="E285" t="s">
+        <v>605</v>
+      </c>
+      <c r="F285" t="s">
+        <v>32</v>
+      </c>
+      <c r="G285" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H285" s="2">
+        <v>151</v>
+      </c>
+      <c r="I285" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J285" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A286" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="B286" t="s">
+        <v>11</v>
+      </c>
+      <c r="C286" t="s">
+        <v>35</v>
+      </c>
+      <c r="D286" t="s">
+        <v>13</v>
+      </c>
+      <c r="E286" t="s">
+        <v>607</v>
+      </c>
+      <c r="F286" t="s">
+        <v>37</v>
+      </c>
+      <c r="G286" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H286" s="2">
+        <v>23</v>
+      </c>
+      <c r="I286" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J286" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A287" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="B287" t="s">
+        <v>11</v>
+      </c>
+      <c r="C287" t="s">
+        <v>39</v>
+      </c>
+      <c r="D287" t="s">
+        <v>13</v>
+      </c>
+      <c r="E287" t="s">
+        <v>609</v>
+      </c>
+      <c r="F287" t="s">
+        <v>41</v>
+      </c>
+      <c r="G287" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H287" s="2">
+        <v>112</v>
+      </c>
+      <c r="I287" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J287" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A288" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B288" t="s">
+        <v>11</v>
+      </c>
+      <c r="C288" t="s">
+        <v>43</v>
+      </c>
+      <c r="D288" t="s">
+        <v>13</v>
+      </c>
+      <c r="E288" t="s">
+        <v>611</v>
+      </c>
+      <c r="F288" t="s">
+        <v>45</v>
+      </c>
+      <c r="G288" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H288" s="2">
+        <v>137</v>
+      </c>
+      <c r="I288" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J288" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A289" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="B289" t="s">
+        <v>11</v>
+      </c>
+      <c r="C289" t="s">
+        <v>47</v>
+      </c>
+      <c r="D289" t="s">
+        <v>13</v>
+      </c>
+      <c r="E289" t="s">
+        <v>613</v>
+      </c>
+      <c r="F289" t="s">
+        <v>49</v>
+      </c>
+      <c r="G289" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H289" s="2">
+        <v>82</v>
+      </c>
+      <c r="I289" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J289" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A290" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B290" t="s">
+        <v>11</v>
+      </c>
+      <c r="C290" t="s">
+        <v>51</v>
+      </c>
+      <c r="D290" t="s">
+        <v>13</v>
+      </c>
+      <c r="E290" t="s">
+        <v>615</v>
+      </c>
+      <c r="F290" t="s">
+        <v>53</v>
+      </c>
+      <c r="G290" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H290" s="2">
+        <v>80</v>
+      </c>
+      <c r="I290" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J290" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A291" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="B291" t="s">
+        <v>11</v>
+      </c>
+      <c r="C291" t="s">
+        <v>55</v>
+      </c>
+      <c r="D291" t="s">
+        <v>13</v>
+      </c>
+      <c r="E291" t="s">
+        <v>617</v>
+      </c>
+      <c r="F291" t="s">
+        <v>57</v>
+      </c>
+      <c r="G291" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H291" s="2">
+        <v>107</v>
+      </c>
+      <c r="I291" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J291" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A292" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="B292" t="s">
+        <v>11</v>
+      </c>
+      <c r="C292" t="s">
+        <v>12</v>
+      </c>
+      <c r="D292" t="s">
+        <v>13</v>
+      </c>
+      <c r="E292" t="s">
+        <v>619</v>
+      </c>
+      <c r="F292" t="s">
+        <v>15</v>
+      </c>
+      <c r="G292" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H292" s="2">
+        <v>47</v>
+      </c>
+      <c r="I292" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J292" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A293" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="B293" t="s">
+        <v>11</v>
+      </c>
+      <c r="C293" t="s">
+        <v>20</v>
+      </c>
+      <c r="D293" t="s">
+        <v>13</v>
+      </c>
+      <c r="E293" t="s">
+        <v>621</v>
+      </c>
+      <c r="F293" t="s">
+        <v>22</v>
+      </c>
+      <c r="G293" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H293" s="2">
+        <v>58</v>
+      </c>
+      <c r="I293" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J293" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A294" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="B294" t="s">
+        <v>11</v>
+      </c>
+      <c r="C294" t="s">
+        <v>25</v>
+      </c>
+      <c r="D294" t="s">
+        <v>13</v>
+      </c>
+      <c r="E294" t="s">
+        <v>623</v>
+      </c>
+      <c r="F294" t="s">
+        <v>27</v>
+      </c>
+      <c r="G294" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H294" s="2">
+        <v>15</v>
+      </c>
+      <c r="I294" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J294" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A295" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="B295" t="s">
+        <v>11</v>
+      </c>
+      <c r="C295" t="s">
+        <v>30</v>
+      </c>
+      <c r="D295" t="s">
+        <v>13</v>
+      </c>
+      <c r="E295" t="s">
+        <v>625</v>
+      </c>
+      <c r="F295" t="s">
+        <v>32</v>
+      </c>
+      <c r="G295" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H295" s="2">
+        <v>72</v>
+      </c>
+      <c r="I295" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J295" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A296" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="B296" t="s">
+        <v>11</v>
+      </c>
+      <c r="C296" t="s">
+        <v>35</v>
+      </c>
+      <c r="D296" t="s">
+        <v>13</v>
+      </c>
+      <c r="E296" t="s">
+        <v>627</v>
+      </c>
+      <c r="F296" t="s">
+        <v>37</v>
+      </c>
+      <c r="G296" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H296" s="2">
+        <v>17</v>
+      </c>
+      <c r="I296" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J296" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A297" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="B297" t="s">
+        <v>11</v>
+      </c>
+      <c r="C297" t="s">
+        <v>39</v>
+      </c>
+      <c r="D297" t="s">
+        <v>13</v>
+      </c>
+      <c r="E297" t="s">
+        <v>629</v>
+      </c>
+      <c r="F297" t="s">
+        <v>41</v>
+      </c>
+      <c r="G297" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H297" s="2">
+        <v>145</v>
+      </c>
+      <c r="I297" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J297" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A298" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="B298" t="s">
+        <v>11</v>
+      </c>
+      <c r="C298" t="s">
+        <v>43</v>
+      </c>
+      <c r="D298" t="s">
+        <v>13</v>
+      </c>
+      <c r="E298" t="s">
+        <v>631</v>
+      </c>
+      <c r="F298" t="s">
+        <v>45</v>
+      </c>
+      <c r="G298" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H298" s="2">
+        <v>111</v>
+      </c>
+      <c r="I298" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J298" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A299" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="B299" t="s">
+        <v>11</v>
+      </c>
+      <c r="C299" t="s">
+        <v>47</v>
+      </c>
+      <c r="D299" t="s">
+        <v>13</v>
+      </c>
+      <c r="E299" t="s">
+        <v>633</v>
+      </c>
+      <c r="F299" t="s">
+        <v>49</v>
+      </c>
+      <c r="G299" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H299" s="2">
+        <v>141</v>
+      </c>
+      <c r="I299" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J299" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A300" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="B300" t="s">
+        <v>11</v>
+      </c>
+      <c r="C300" t="s">
+        <v>51</v>
+      </c>
+      <c r="D300" t="s">
+        <v>13</v>
+      </c>
+      <c r="E300" t="s">
+        <v>635</v>
+      </c>
+      <c r="F300" t="s">
+        <v>53</v>
+      </c>
+      <c r="G300" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H300" s="2">
+        <v>128</v>
+      </c>
+      <c r="I300" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J300" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A301" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="B301" t="s">
+        <v>11</v>
+      </c>
+      <c r="C301" t="s">
+        <v>55</v>
+      </c>
+      <c r="D301" t="s">
+        <v>13</v>
+      </c>
+      <c r="E301" t="s">
+        <v>637</v>
+      </c>
+      <c r="F301" t="s">
+        <v>57</v>
+      </c>
+      <c r="G301" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H301" s="2">
+        <v>67</v>
+      </c>
+      <c r="I301" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J301" t="s">
         <v>18</v>
       </c>
     </row>
